--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -2106,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122719953</v>
+        <v>122719455</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>79843</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2122,21 +2122,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580942</v>
+        <v>580912</v>
       </c>
       <c r="R15" t="n">
-        <v>7057618</v>
+        <v>7057652</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,9 +2179,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,19 +2206,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122719455</v>
+        <v>122721504</v>
       </c>
       <c r="B16" t="n">
         <v>79843</v>
@@ -2244,14 +2254,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580912</v>
+        <v>581165</v>
       </c>
       <c r="R16" t="n">
-        <v>7057652</v>
+        <v>7057471</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2293,7 +2303,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,22 +2318,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122721504</v>
+        <v>122719953</v>
       </c>
       <c r="B17" t="n">
-        <v>79843</v>
+        <v>78762</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2336,34 +2346,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581165</v>
+        <v>580942</v>
       </c>
       <c r="R17" t="n">
-        <v>7057471</v>
+        <v>7057618</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,19 +2403,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2420,12 +2420,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3913,10 +3913,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122722549</v>
+        <v>122721705</v>
       </c>
       <c r="B31" t="n">
-        <v>78762</v>
+        <v>78498</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3929,21 +3929,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581043</v>
+        <v>581182</v>
       </c>
       <c r="R31" t="n">
-        <v>7057689</v>
+        <v>7057497</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4013,22 +4013,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122721705</v>
+        <v>122722549</v>
       </c>
       <c r="B32" t="n">
-        <v>78498</v>
+        <v>78762</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4041,21 +4041,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581182</v>
+        <v>581043</v>
       </c>
       <c r="R32" t="n">
-        <v>7057497</v>
+        <v>7057689</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4125,12 +4125,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122719130</v>
+        <v>122720911</v>
       </c>
       <c r="B35" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580985</v>
+        <v>581101</v>
       </c>
       <c r="R35" t="n">
-        <v>7057694</v>
+        <v>7057443</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4451,7 +4451,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4466,22 +4471,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122720911</v>
+        <v>122719130</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4494,21 +4499,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4518,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581101</v>
+        <v>580985</v>
       </c>
       <c r="R36" t="n">
-        <v>7057443</v>
+        <v>7057694</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4553,7 +4558,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4563,12 +4568,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,12 +4583,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122722473</v>
+        <v>122721034</v>
       </c>
       <c r="B47" t="n">
-        <v>78762</v>
+        <v>78499</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5741,21 +5741,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581086</v>
+        <v>581112</v>
       </c>
       <c r="R47" t="n">
-        <v>7057686</v>
+        <v>7057450</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5825,19 +5825,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122719411</v>
+        <v>122722473</v>
       </c>
       <c r="B48" t="n">
         <v>78762</v>
@@ -5873,17 +5873,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580961</v>
+        <v>581086</v>
       </c>
       <c r="R48" t="n">
-        <v>7057655</v>
+        <v>7057686</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5937,22 +5937,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122721034</v>
+        <v>122719411</v>
       </c>
       <c r="B49" t="n">
-        <v>78499</v>
+        <v>78762</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5965,37 +5965,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581112</v>
+        <v>580961</v>
       </c>
       <c r="R49" t="n">
-        <v>7057450</v>
+        <v>7057655</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122721338</v>
       </c>
       <c r="B2" t="n">
-        <v>78498</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721501</v>
+        <v>122721113</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581145</v>
+        <v>581208</v>
       </c>
       <c r="R3" t="n">
-        <v>7057410</v>
+        <v>7057415</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721113</v>
+        <v>122721501</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,42 +920,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581208</v>
+        <v>581145</v>
       </c>
       <c r="R4" t="n">
-        <v>7057415</v>
+        <v>7057410</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122720528</v>
+        <v>122720478</v>
       </c>
       <c r="B5" t="n">
-        <v>78499</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581073</v>
+        <v>581116</v>
       </c>
       <c r="R5" t="n">
-        <v>7057503</v>
+        <v>7057570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122719696</v>
+        <v>122720827</v>
       </c>
       <c r="B6" t="n">
-        <v>78407</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580901</v>
+        <v>581102</v>
       </c>
       <c r="R6" t="n">
-        <v>7057649</v>
+        <v>7057553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122720544</v>
+        <v>122721746</v>
       </c>
       <c r="B7" t="n">
-        <v>78498</v>
+        <v>91389</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,25 +1252,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581116</v>
+        <v>581131</v>
       </c>
       <c r="R7" t="n">
-        <v>7057570</v>
+        <v>7057499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,22 +1340,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122718574</v>
+        <v>122719175</v>
       </c>
       <c r="B8" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580996</v>
+        <v>580984</v>
       </c>
       <c r="R8" t="n">
-        <v>7057711</v>
+        <v>7057676</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1452,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122719973</v>
+        <v>122719400</v>
       </c>
       <c r="B9" t="n">
-        <v>78498</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580942</v>
+        <v>580956</v>
       </c>
       <c r="R9" t="n">
-        <v>7057618</v>
+        <v>7057671</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122719531</v>
+        <v>122721003</v>
       </c>
       <c r="B10" t="n">
-        <v>79844</v>
+        <v>78502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580913</v>
+        <v>581112</v>
       </c>
       <c r="R10" t="n">
-        <v>7057655</v>
+        <v>7057450</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1666,22 +1666,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122720351</v>
+        <v>122721690</v>
       </c>
       <c r="B11" t="n">
-        <v>78762</v>
+        <v>91389</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,25 +1690,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581082</v>
+        <v>581129</v>
       </c>
       <c r="R11" t="n">
-        <v>7057561</v>
+        <v>7057525</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,22 +1778,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122721195</v>
+        <v>122721757</v>
       </c>
       <c r="B12" t="n">
-        <v>79843</v>
+        <v>91235</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581116</v>
+        <v>581120</v>
       </c>
       <c r="R12" t="n">
-        <v>7057434</v>
+        <v>7057493</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,9 +1863,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,22 +1890,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122720063</v>
+        <v>122721655</v>
       </c>
       <c r="B13" t="n">
-        <v>78498</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,13 +1942,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580986</v>
+        <v>581182</v>
       </c>
       <c r="R13" t="n">
-        <v>7057585</v>
+        <v>7057497</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,22 +2002,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122719444</v>
+        <v>122722057</v>
       </c>
       <c r="B14" t="n">
-        <v>78498</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,34 +2030,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580956</v>
+        <v>581149</v>
       </c>
       <c r="R14" t="n">
-        <v>7057671</v>
+        <v>7057577</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,9 +2092,24 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,22 +2124,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122719455</v>
+        <v>122720457</v>
       </c>
       <c r="B15" t="n">
-        <v>79843</v>
+        <v>57494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2122,34 +2152,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580912</v>
+        <v>581081</v>
       </c>
       <c r="R15" t="n">
-        <v>7057652</v>
+        <v>7057535</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2181,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2191,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,22 +2241,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122721504</v>
+        <v>122722071</v>
       </c>
       <c r="B16" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2234,34 +2269,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581165</v>
+        <v>581148</v>
       </c>
       <c r="R16" t="n">
-        <v>7057471</v>
+        <v>7057575</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,7 +2343,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122719953</v>
+        <v>122720546</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,34 +2391,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580942</v>
+        <v>581075</v>
       </c>
       <c r="R17" t="n">
-        <v>7057618</v>
+        <v>7057498</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,9 +2453,24 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2420,22 +2485,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122720827</v>
+        <v>122718574</v>
       </c>
       <c r="B18" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2448,21 +2513,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581102</v>
+        <v>580996</v>
       </c>
       <c r="R18" t="n">
-        <v>7057553</v>
+        <v>7057711</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2507,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2517,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,22 +2597,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122720864</v>
+        <v>122719600</v>
       </c>
       <c r="B19" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,17 +2645,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581112</v>
+        <v>580956</v>
       </c>
       <c r="R19" t="n">
-        <v>7057450</v>
+        <v>7057671</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,21 +2682,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2640,26 +2695,41 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122719600</v>
+        <v>122722549</v>
       </c>
       <c r="B20" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2672,34 +2742,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580956</v>
+        <v>581043</v>
       </c>
       <c r="R20" t="n">
-        <v>7057671</v>
+        <v>7057689</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2729,11 +2799,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2742,41 +2822,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122719558</v>
+        <v>122720577</v>
       </c>
       <c r="B21" t="n">
-        <v>79844</v>
+        <v>78411</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2789,34 +2854,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580907</v>
+        <v>581103</v>
       </c>
       <c r="R21" t="n">
-        <v>7057652</v>
+        <v>7057525</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2848,7 +2913,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2858,7 +2923,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2885,10 +2950,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122722336</v>
+        <v>122721907</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2901,16 +2966,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2930,10 +2995,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581102</v>
+        <v>581134</v>
       </c>
       <c r="R22" t="n">
-        <v>7057625</v>
+        <v>7057504</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2965,7 +3030,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2975,12 +3040,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,10 +3067,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122720096</v>
+        <v>122718748</v>
       </c>
       <c r="B23" t="n">
-        <v>79843</v>
+        <v>56688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3019,38 +3079,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580942</v>
+        <v>581004</v>
       </c>
       <c r="R23" t="n">
-        <v>7057618</v>
+        <v>7057692</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3080,11 +3145,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3093,41 +3168,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122719400</v>
+        <v>122721161</v>
       </c>
       <c r="B24" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3140,21 +3200,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3164,10 +3224,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580956</v>
+        <v>581208</v>
       </c>
       <c r="R24" t="n">
-        <v>7057671</v>
+        <v>7057450</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3197,9 +3257,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3214,22 +3284,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122718499</v>
+        <v>122720458</v>
       </c>
       <c r="B25" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3266,10 +3336,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580999</v>
+        <v>581098</v>
       </c>
       <c r="R25" t="n">
-        <v>7057695</v>
+        <v>7057575</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3301,7 +3371,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3311,7 +3381,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3326,22 +3396,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122722071</v>
+        <v>122721034</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3354,39 +3424,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581148</v>
+        <v>581112</v>
       </c>
       <c r="R26" t="n">
-        <v>7057575</v>
+        <v>7057450</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3418,7 +3483,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3428,12 +3493,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3448,22 +3508,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122720478</v>
+        <v>122722473</v>
       </c>
       <c r="B27" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3500,10 +3560,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581116</v>
+        <v>581086</v>
       </c>
       <c r="R27" t="n">
-        <v>7057570</v>
+        <v>7057686</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3535,7 +3595,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3545,7 +3605,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3560,22 +3620,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122721746</v>
+        <v>122719358</v>
       </c>
       <c r="B28" t="n">
-        <v>91385</v>
+        <v>78502</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3584,38 +3644,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581131</v>
+        <v>580961</v>
       </c>
       <c r="R28" t="n">
-        <v>7057499</v>
+        <v>7057655</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3647,7 +3707,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3657,7 +3717,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3672,22 +3732,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122718748</v>
+        <v>122720864</v>
       </c>
       <c r="B29" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3696,46 +3756,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581004</v>
+        <v>581112</v>
       </c>
       <c r="R29" t="n">
-        <v>7057692</v>
+        <v>7057450</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3764,7 +3819,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3774,7 +3829,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3789,22 +3844,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122719175</v>
+        <v>122719461</v>
       </c>
       <c r="B30" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3817,37 +3872,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580984</v>
+        <v>580912</v>
       </c>
       <c r="R30" t="n">
-        <v>7057676</v>
+        <v>7057652</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3876,7 +3931,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3886,7 +3941,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3913,10 +3968,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122721705</v>
+        <v>122719828</v>
       </c>
       <c r="B31" t="n">
-        <v>78498</v>
+        <v>56688</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3925,38 +3980,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581182</v>
+        <v>580901</v>
       </c>
       <c r="R31" t="n">
-        <v>7057497</v>
+        <v>7057649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3988,7 +4048,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3998,7 +4058,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4025,10 +4085,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122722549</v>
+        <v>122719214</v>
       </c>
       <c r="B32" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4037,41 +4097,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581043</v>
+        <v>580978</v>
       </c>
       <c r="R32" t="n">
-        <v>7057689</v>
+        <v>7057665</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4100,7 +4165,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4110,7 +4175,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4125,22 +4190,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122719585</v>
+        <v>122722701</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4153,37 +4218,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580901</v>
+        <v>581065</v>
       </c>
       <c r="R33" t="n">
-        <v>7057649</v>
+        <v>7057691</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4212,7 +4282,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4222,7 +4292,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4249,10 +4319,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122719828</v>
+        <v>122722336</v>
       </c>
       <c r="B34" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4261,43 +4331,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580901</v>
+        <v>581102</v>
       </c>
       <c r="R34" t="n">
-        <v>7057649</v>
+        <v>7057625</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4329,7 +4399,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4339,7 +4409,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4354,22 +4429,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122720911</v>
+        <v>122719531</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,21 +4457,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4406,10 +4481,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581101</v>
+        <v>580913</v>
       </c>
       <c r="R35" t="n">
-        <v>7057443</v>
+        <v>7057655</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4441,7 +4516,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4451,12 +4526,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4471,22 +4541,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122719130</v>
+        <v>122720351</v>
       </c>
       <c r="B36" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4499,21 +4569,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4593,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580985</v>
+        <v>581082</v>
       </c>
       <c r="R36" t="n">
-        <v>7057694</v>
+        <v>7057561</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4558,7 +4628,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4638,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,22 +4653,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122721690</v>
+        <v>122718678</v>
       </c>
       <c r="B37" t="n">
-        <v>91385</v>
+        <v>78502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4607,25 +4677,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4635,10 +4705,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581129</v>
+        <v>581005</v>
       </c>
       <c r="R37" t="n">
-        <v>7057525</v>
+        <v>7057691</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4670,7 +4740,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4680,7 +4750,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4707,10 +4777,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122722537</v>
+        <v>122719130</v>
       </c>
       <c r="B38" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4723,21 +4793,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4747,10 +4817,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581065</v>
+        <v>580985</v>
       </c>
       <c r="R38" t="n">
-        <v>7057691</v>
+        <v>7057694</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4782,7 +4852,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4792,7 +4862,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4807,22 +4877,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122720361</v>
+        <v>122722537</v>
       </c>
       <c r="B39" t="n">
-        <v>78498</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4835,21 +4905,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4859,13 +4929,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581082</v>
+        <v>581065</v>
       </c>
       <c r="R39" t="n">
-        <v>7057561</v>
+        <v>7057691</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4894,7 +4964,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4904,7 +4974,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4931,10 +5001,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122720458</v>
+        <v>122721705</v>
       </c>
       <c r="B40" t="n">
-        <v>78762</v>
+        <v>78502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4947,21 +5017,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4971,10 +5041,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581098</v>
+        <v>581182</v>
       </c>
       <c r="R40" t="n">
-        <v>7057575</v>
+        <v>7057497</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5006,7 +5076,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5016,7 +5086,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5043,10 +5113,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122722568</v>
+        <v>122719558</v>
       </c>
       <c r="B41" t="n">
-        <v>78762</v>
+        <v>79848</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5059,34 +5129,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581036</v>
+        <v>580907</v>
       </c>
       <c r="R41" t="n">
-        <v>7057698</v>
+        <v>7057652</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5118,7 +5188,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5128,7 +5198,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5143,22 +5213,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122722701</v>
+        <v>122720366</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>78503</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5171,42 +5241,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581065</v>
+        <v>581078</v>
       </c>
       <c r="R42" t="n">
-        <v>7057691</v>
+        <v>7057568</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5235,7 +5300,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5245,7 +5310,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5272,10 +5337,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122718678</v>
+        <v>122722222</v>
       </c>
       <c r="B43" t="n">
-        <v>78498</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5288,34 +5353,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581005</v>
+        <v>581129</v>
       </c>
       <c r="R43" t="n">
-        <v>7057691</v>
+        <v>7057634</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5347,7 +5417,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5357,7 +5427,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5384,10 +5459,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122721907</v>
+        <v>122719411</v>
       </c>
       <c r="B44" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5400,42 +5475,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581134</v>
+        <v>580961</v>
       </c>
       <c r="R44" t="n">
-        <v>7057504</v>
+        <v>7057655</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5464,7 +5534,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5474,7 +5544,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5489,22 +5559,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122719250</v>
+        <v>122718499</v>
       </c>
       <c r="B45" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5517,21 +5587,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5541,10 +5611,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580977</v>
+        <v>580999</v>
       </c>
       <c r="R45" t="n">
-        <v>7057668</v>
+        <v>7057695</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5576,7 +5646,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5586,7 +5656,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5613,10 +5683,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122721161</v>
+        <v>122720278</v>
       </c>
       <c r="B46" t="n">
-        <v>79843</v>
+        <v>78502</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5629,21 +5699,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5653,10 +5723,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581208</v>
+        <v>580942</v>
       </c>
       <c r="R46" t="n">
-        <v>7057450</v>
+        <v>7057618</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5686,19 +5756,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5713,22 +5773,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122721034</v>
+        <v>122720911</v>
       </c>
       <c r="B47" t="n">
-        <v>78499</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5741,21 +5801,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5765,10 +5825,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581112</v>
+        <v>581101</v>
       </c>
       <c r="R47" t="n">
-        <v>7057450</v>
+        <v>7057443</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5800,7 +5860,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5810,7 +5870,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5825,22 +5890,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122722473</v>
+        <v>122721195</v>
       </c>
       <c r="B48" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5853,21 +5918,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5877,10 +5942,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581086</v>
+        <v>581116</v>
       </c>
       <c r="R48" t="n">
-        <v>7057686</v>
+        <v>7057434</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5910,19 +5975,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5937,22 +5992,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122719411</v>
+        <v>122718715</v>
       </c>
       <c r="B49" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5965,37 +6020,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580961</v>
+        <v>581011</v>
       </c>
       <c r="R49" t="n">
-        <v>7057655</v>
+        <v>7057695</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6024,7 +6079,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6034,7 +6089,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6049,22 +6104,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122719358</v>
+        <v>122719585</v>
       </c>
       <c r="B50" t="n">
-        <v>78498</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6077,21 +6132,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6101,10 +6156,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580961</v>
+        <v>580901</v>
       </c>
       <c r="R50" t="n">
-        <v>7057655</v>
+        <v>7057649</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6136,7 +6191,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6146,7 +6201,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6173,10 +6228,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122722057</v>
+        <v>122719696</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>78411</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6189,39 +6244,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581149</v>
+        <v>580901</v>
       </c>
       <c r="R51" t="n">
-        <v>7057577</v>
+        <v>7057649</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6253,7 +6303,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6263,12 +6313,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6283,22 +6328,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122722222</v>
+        <v>122720528</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6311,39 +6356,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581129</v>
+        <v>581073</v>
       </c>
       <c r="R52" t="n">
-        <v>7057634</v>
+        <v>7057503</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6375,7 +6415,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6385,12 +6425,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6405,22 +6440,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122721003</v>
+        <v>122719953</v>
       </c>
       <c r="B53" t="n">
-        <v>78498</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6433,37 +6468,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581112</v>
+        <v>580942</v>
       </c>
       <c r="R53" t="n">
-        <v>7057450</v>
+        <v>7057618</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,19 +6525,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6517,22 +6542,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122720457</v>
+        <v>122722568</v>
       </c>
       <c r="B54" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6545,39 +6570,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581081</v>
+        <v>581036</v>
       </c>
       <c r="R54" t="n">
-        <v>7057535</v>
+        <v>7057698</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6609,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6619,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6646,10 +6666,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122722059</v>
+        <v>122719250</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6662,21 +6682,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6686,10 +6706,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581149</v>
+        <v>580977</v>
       </c>
       <c r="R55" t="n">
-        <v>7057571</v>
+        <v>7057668</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6721,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6731,12 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6751,22 +6766,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122720577</v>
+        <v>122720361</v>
       </c>
       <c r="B56" t="n">
-        <v>78407</v>
+        <v>78502</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6779,21 +6794,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6803,13 +6818,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581103</v>
+        <v>581082</v>
       </c>
       <c r="R56" t="n">
-        <v>7057525</v>
+        <v>7057561</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6875,10 +6890,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122719963</v>
+        <v>122720063</v>
       </c>
       <c r="B57" t="n">
-        <v>78498</v>
+        <v>78502</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6911,14 +6926,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>580966</v>
+        <v>580986</v>
       </c>
       <c r="R57" t="n">
-        <v>7057594</v>
+        <v>7057585</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6950,7 +6965,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6960,7 +6975,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6975,22 +6990,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122720546</v>
+        <v>122721504</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7003,39 +7018,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581075</v>
+        <v>581165</v>
       </c>
       <c r="R58" t="n">
-        <v>7057498</v>
+        <v>7057471</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7067,7 +7077,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7077,12 +7087,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7109,10 +7114,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122720366</v>
+        <v>122719963</v>
       </c>
       <c r="B59" t="n">
-        <v>78499</v>
+        <v>78502</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7125,34 +7130,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581078</v>
+        <v>580966</v>
       </c>
       <c r="R59" t="n">
-        <v>7057568</v>
+        <v>7057594</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7184,7 +7189,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7194,7 +7199,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7221,10 +7226,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122718715</v>
+        <v>122722059</v>
       </c>
       <c r="B60" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7237,21 +7242,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7261,10 +7266,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581011</v>
+        <v>581149</v>
       </c>
       <c r="R60" t="n">
-        <v>7057695</v>
+        <v>7057571</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7296,7 +7301,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7306,7 +7311,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7321,22 +7331,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122721655</v>
+        <v>122720544</v>
       </c>
       <c r="B61" t="n">
-        <v>78762</v>
+        <v>78502</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7349,21 +7359,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7373,13 +7383,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581182</v>
+        <v>581116</v>
       </c>
       <c r="R61" t="n">
-        <v>7057497</v>
+        <v>7057570</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7408,7 +7418,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7418,7 +7428,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7445,10 +7455,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122719214</v>
+        <v>122719444</v>
       </c>
       <c r="B62" t="n">
-        <v>56688</v>
+        <v>78502</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7457,46 +7467,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580978</v>
+        <v>580956</v>
       </c>
       <c r="R62" t="n">
-        <v>7057665</v>
+        <v>7057671</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7523,19 +7528,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7550,22 +7545,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122721757</v>
+        <v>122720096</v>
       </c>
       <c r="B63" t="n">
-        <v>91231</v>
+        <v>79847</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7578,34 +7573,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581120</v>
+        <v>580942</v>
       </c>
       <c r="R63" t="n">
-        <v>7057493</v>
+        <v>7057618</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7635,21 +7630,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7658,16 +7643,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122721690</v>
+        <v>122721655</v>
       </c>
       <c r="B11" t="n">
-        <v>91389</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,25 +1690,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581129</v>
+        <v>581182</v>
       </c>
       <c r="R11" t="n">
-        <v>7057525</v>
+        <v>7057497</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,22 +1778,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122721757</v>
+        <v>122721690</v>
       </c>
       <c r="B12" t="n">
-        <v>91235</v>
+        <v>91389</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,25 +1802,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581120</v>
+        <v>581129</v>
       </c>
       <c r="R12" t="n">
-        <v>7057493</v>
+        <v>7057525</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,22 +1890,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122721655</v>
+        <v>122721757</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581182</v>
+        <v>581120</v>
       </c>
       <c r="R13" t="n">
-        <v>7057497</v>
+        <v>7057493</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2002,12 +2002,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122718748</v>
+        <v>122720458</v>
       </c>
       <c r="B23" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,43 +3079,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581004</v>
+        <v>581098</v>
       </c>
       <c r="R23" t="n">
-        <v>7057692</v>
+        <v>7057575</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3147,7 +3142,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3157,7 +3152,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,22 +3167,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122721161</v>
+        <v>122721034</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3200,31 +3195,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581208</v>
+        <v>581112</v>
       </c>
       <c r="R24" t="n">
         <v>7057450</v>
@@ -3259,7 +3254,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3269,7 +3264,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3284,22 +3279,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122720458</v>
+        <v>122718748</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3308,38 +3303,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581098</v>
+        <v>581004</v>
       </c>
       <c r="R25" t="n">
-        <v>7057575</v>
+        <v>7057692</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3396,22 +3396,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122721034</v>
+        <v>122721161</v>
       </c>
       <c r="B26" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3424,31 +3424,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581112</v>
+        <v>581208</v>
       </c>
       <c r="R26" t="n">
         <v>7057450</v>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3508,22 +3508,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122722473</v>
+        <v>122720864</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3536,21 +3536,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3560,13 +3560,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581086</v>
+        <v>581112</v>
       </c>
       <c r="R27" t="n">
-        <v>7057686</v>
+        <v>7057450</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3620,22 +3620,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122719358</v>
+        <v>122719461</v>
       </c>
       <c r="B28" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580961</v>
+        <v>580912</v>
       </c>
       <c r="R28" t="n">
-        <v>7057655</v>
+        <v>7057652</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3744,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122720864</v>
+        <v>122722473</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3784,13 +3784,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581112</v>
+        <v>581086</v>
       </c>
       <c r="R29" t="n">
-        <v>7057450</v>
+        <v>7057686</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3844,22 +3844,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122719461</v>
+        <v>122719358</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3872,21 +3872,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580912</v>
+        <v>580961</v>
       </c>
       <c r="R30" t="n">
-        <v>7057652</v>
+        <v>7057655</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4202,10 +4202,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122722701</v>
+        <v>122718678</v>
       </c>
       <c r="B33" t="n">
-        <v>57494</v>
+        <v>78502</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4218,42 +4218,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581065</v>
+        <v>581005</v>
       </c>
       <c r="R33" t="n">
         <v>7057691</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4282,7 +4277,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4292,7 +4287,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4307,22 +4302,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122722336</v>
+        <v>122719130</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4335,39 +4330,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581102</v>
+        <v>580985</v>
       </c>
       <c r="R34" t="n">
-        <v>7057625</v>
+        <v>7057694</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4399,7 +4389,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4409,12 +4399,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4441,10 +4426,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122719531</v>
+        <v>122722701</v>
       </c>
       <c r="B35" t="n">
-        <v>79848</v>
+        <v>57494</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4457,37 +4442,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580913</v>
+        <v>581065</v>
       </c>
       <c r="R35" t="n">
-        <v>7057655</v>
+        <v>7057691</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4516,7 +4506,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4526,7 +4516,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4541,22 +4531,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122720351</v>
+        <v>122722336</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4569,34 +4559,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581082</v>
+        <v>581102</v>
       </c>
       <c r="R36" t="n">
-        <v>7057561</v>
+        <v>7057625</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4628,7 +4623,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4638,7 +4633,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4653,22 +4653,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122718678</v>
+        <v>122720351</v>
       </c>
       <c r="B37" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4681,21 +4681,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4705,10 +4705,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581005</v>
+        <v>581082</v>
       </c>
       <c r="R37" t="n">
-        <v>7057691</v>
+        <v>7057561</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4765,22 +4765,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122719130</v>
+        <v>122719531</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4793,21 +4793,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4817,10 +4817,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580985</v>
+        <v>580913</v>
       </c>
       <c r="R38" t="n">
-        <v>7057694</v>
+        <v>7057655</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4889,10 +4889,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122722537</v>
+        <v>122720366</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4905,21 +4905,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581065</v>
+        <v>581078</v>
       </c>
       <c r="R39" t="n">
-        <v>7057691</v>
+        <v>7057568</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5001,10 +5001,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122721705</v>
+        <v>122722537</v>
       </c>
       <c r="B40" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581182</v>
+        <v>581065</v>
       </c>
       <c r="R40" t="n">
-        <v>7057497</v>
+        <v>7057691</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5113,10 +5113,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122719558</v>
+        <v>122721705</v>
       </c>
       <c r="B41" t="n">
-        <v>79848</v>
+        <v>78502</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5129,34 +5129,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580907</v>
+        <v>581182</v>
       </c>
       <c r="R41" t="n">
-        <v>7057652</v>
+        <v>7057497</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5225,10 +5225,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122720366</v>
+        <v>122719558</v>
       </c>
       <c r="B42" t="n">
-        <v>78503</v>
+        <v>79848</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5241,34 +5241,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581078</v>
+        <v>580907</v>
       </c>
       <c r="R42" t="n">
-        <v>7057568</v>
+        <v>7057652</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -7002,10 +7002,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122721504</v>
+        <v>122719963</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7018,34 +7018,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581165</v>
+        <v>580966</v>
       </c>
       <c r="R58" t="n">
-        <v>7057471</v>
+        <v>7057594</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7102,22 +7102,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122719963</v>
+        <v>122721504</v>
       </c>
       <c r="B59" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7130,34 +7130,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580966</v>
+        <v>581165</v>
       </c>
       <c r="R59" t="n">
-        <v>7057594</v>
+        <v>7057471</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7214,22 +7214,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122722059</v>
+        <v>122720544</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7242,21 +7242,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7266,10 +7266,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581149</v>
+        <v>581116</v>
       </c>
       <c r="R60" t="n">
-        <v>7057571</v>
+        <v>7057570</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7311,12 +7311,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7331,22 +7326,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122720544</v>
+        <v>122722059</v>
       </c>
       <c r="B61" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7359,21 +7354,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7383,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581116</v>
+        <v>581149</v>
       </c>
       <c r="R61" t="n">
-        <v>7057570</v>
+        <v>7057571</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7418,7 +7413,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7428,7 +7423,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7443,12 +7443,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122721338</v>
+        <v>122721501</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,7 +721,7 @@
         <v>7057410</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721501</v>
+        <v>122721338</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,7 +950,7 @@
         <v>7057410</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122720478</v>
+        <v>122719696</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581116</v>
+        <v>580901</v>
       </c>
       <c r="R5" t="n">
-        <v>7057570</v>
+        <v>7057649</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122720827</v>
+        <v>122719585</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1164,14 +1164,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581102</v>
+        <v>580901</v>
       </c>
       <c r="R6" t="n">
-        <v>7057553</v>
+        <v>7057649</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122721746</v>
+        <v>122721655</v>
       </c>
       <c r="B7" t="n">
-        <v>91389</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,25 +1252,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581131</v>
+        <v>581182</v>
       </c>
       <c r="R7" t="n">
-        <v>7057499</v>
+        <v>7057497</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,22 +1340,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122719175</v>
+        <v>122719358</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,37 +1368,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580984</v>
+        <v>580961</v>
       </c>
       <c r="R8" t="n">
-        <v>7057676</v>
+        <v>7057655</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122719400</v>
+        <v>122719600</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1550,6 +1550,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1566,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122721003</v>
+        <v>122721504</v>
       </c>
       <c r="B10" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,21 +1597,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,13 +1621,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581112</v>
+        <v>581165</v>
       </c>
       <c r="R10" t="n">
-        <v>7057450</v>
+        <v>7057471</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1666,22 +1681,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122721655</v>
+        <v>122721034</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,21 +1709,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,13 +1733,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581182</v>
+        <v>581112</v>
       </c>
       <c r="R11" t="n">
-        <v>7057497</v>
+        <v>7057450</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122721690</v>
+        <v>122720457</v>
       </c>
       <c r="B12" t="n">
-        <v>91389</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,38 +1817,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581129</v>
+        <v>581081</v>
       </c>
       <c r="R12" t="n">
-        <v>7057525</v>
+        <v>7057535</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,22 +1910,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122721757</v>
+        <v>122720096</v>
       </c>
       <c r="B13" t="n">
-        <v>91235</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,34 +1938,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581120</v>
+        <v>580942</v>
       </c>
       <c r="R13" t="n">
-        <v>7057493</v>
+        <v>7057618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,21 +1995,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1998,26 +2008,41 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122722057</v>
+        <v>122721690</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>91389</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,43 +2051,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581149</v>
+        <v>581129</v>
       </c>
       <c r="R14" t="n">
-        <v>7057577</v>
+        <v>7057525</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,12 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122720457</v>
+        <v>122721757</v>
       </c>
       <c r="B15" t="n">
-        <v>57494</v>
+        <v>91235</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,39 +2167,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581081</v>
+        <v>581120</v>
       </c>
       <c r="R15" t="n">
-        <v>7057535</v>
+        <v>7057493</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122722071</v>
+        <v>122719442</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,39 +2279,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581148</v>
+        <v>580912</v>
       </c>
       <c r="R16" t="n">
-        <v>7057575</v>
+        <v>7057652</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,12 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,22 +2363,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122720546</v>
+        <v>122720458</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,39 +2391,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581075</v>
+        <v>581098</v>
       </c>
       <c r="R17" t="n">
-        <v>7057498</v>
+        <v>7057575</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2455,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,12 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,19 +2475,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122718574</v>
+        <v>122721161</v>
       </c>
       <c r="B18" t="n">
         <v>79847</v>
@@ -2533,14 +2523,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580996</v>
+        <v>581208</v>
       </c>
       <c r="R18" t="n">
-        <v>7057711</v>
+        <v>7057450</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2572,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,22 +2587,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122719600</v>
+        <v>122720827</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2625,34 +2615,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580956</v>
+        <v>581102</v>
       </c>
       <c r="R19" t="n">
-        <v>7057671</v>
+        <v>7057553</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2682,11 +2672,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2695,41 +2695,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122722549</v>
+        <v>122721746</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>91389</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2738,25 +2723,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2766,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581043</v>
+        <v>581131</v>
       </c>
       <c r="R20" t="n">
-        <v>7057689</v>
+        <v>7057499</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2801,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2811,7 +2796,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2826,22 +2811,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122720577</v>
+        <v>122720546</v>
       </c>
       <c r="B21" t="n">
-        <v>78411</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2854,34 +2839,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581103</v>
+        <v>581075</v>
       </c>
       <c r="R21" t="n">
-        <v>7057525</v>
+        <v>7057498</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2913,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2923,7 +2913,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,22 +2933,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122721907</v>
+        <v>122719963</v>
       </c>
       <c r="B22" t="n">
-        <v>57494</v>
+        <v>78502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2966,39 +2961,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581134</v>
+        <v>580966</v>
       </c>
       <c r="R22" t="n">
-        <v>7057504</v>
+        <v>7057594</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3030,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3040,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3055,22 +3045,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122720458</v>
+        <v>122719214</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,41 +3069,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581098</v>
+        <v>580978</v>
       </c>
       <c r="R23" t="n">
-        <v>7057575</v>
+        <v>7057665</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3142,7 +3137,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3152,7 +3147,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3179,10 +3174,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122721034</v>
+        <v>122719531</v>
       </c>
       <c r="B24" t="n">
-        <v>78503</v>
+        <v>79848</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3195,21 +3190,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3219,10 +3214,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581112</v>
+        <v>580913</v>
       </c>
       <c r="R24" t="n">
-        <v>7057450</v>
+        <v>7057655</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,7 +3249,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3264,7 +3259,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3279,22 +3274,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122718748</v>
+        <v>122720864</v>
       </c>
       <c r="B25" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3303,46 +3298,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581004</v>
+        <v>581112</v>
       </c>
       <c r="R25" t="n">
-        <v>7057692</v>
+        <v>7057450</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3371,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3381,7 +3371,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3396,22 +3386,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122721161</v>
+        <v>122722701</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3424,37 +3414,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581208</v>
+        <v>581065</v>
       </c>
       <c r="R26" t="n">
-        <v>7057450</v>
+        <v>7057691</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3483,7 +3478,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3493,7 +3488,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3508,22 +3503,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122720864</v>
+        <v>122722336</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3536,37 +3531,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581112</v>
+        <v>581102</v>
       </c>
       <c r="R27" t="n">
-        <v>7057450</v>
+        <v>7057625</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3605,7 +3605,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3620,22 +3625,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122719461</v>
+        <v>122722222</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3648,34 +3653,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580912</v>
+        <v>581129</v>
       </c>
       <c r="R28" t="n">
-        <v>7057652</v>
+        <v>7057634</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3707,7 +3717,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3717,7 +3727,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3732,22 +3747,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122722473</v>
+        <v>122720528</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,21 +3775,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3784,10 +3799,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581086</v>
+        <v>581073</v>
       </c>
       <c r="R29" t="n">
-        <v>7057686</v>
+        <v>7057503</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3819,7 +3834,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3829,7 +3844,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3844,22 +3859,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122719358</v>
+        <v>122719250</v>
       </c>
       <c r="B30" t="n">
-        <v>78502</v>
+        <v>90944</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3872,34 +3887,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580961</v>
+        <v>580977</v>
       </c>
       <c r="R30" t="n">
-        <v>7057655</v>
+        <v>7057668</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3931,7 +3946,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3941,7 +3956,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3956,22 +3971,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122719828</v>
+        <v>122720911</v>
       </c>
       <c r="B31" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3980,43 +3995,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580901</v>
+        <v>581101</v>
       </c>
       <c r="R31" t="n">
-        <v>7057649</v>
+        <v>7057443</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4048,7 +4058,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4058,7 +4068,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4073,22 +4088,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122719214</v>
+        <v>122722071</v>
       </c>
       <c r="B32" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4097,31 +4112,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4130,13 +4145,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580978</v>
+        <v>581148</v>
       </c>
       <c r="R32" t="n">
-        <v>7057665</v>
+        <v>7057575</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4165,7 +4180,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4175,7 +4190,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4190,22 +4210,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122718678</v>
+        <v>122722549</v>
       </c>
       <c r="B33" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4218,21 +4238,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4242,10 +4262,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581005</v>
+        <v>581043</v>
       </c>
       <c r="R33" t="n">
-        <v>7057691</v>
+        <v>7057689</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4277,7 +4297,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4287,7 +4307,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4314,10 +4334,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122719130</v>
+        <v>122722568</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4330,21 +4350,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4354,10 +4374,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580985</v>
+        <v>581036</v>
       </c>
       <c r="R34" t="n">
-        <v>7057694</v>
+        <v>7057698</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4389,7 +4409,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4399,7 +4419,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4414,22 +4434,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122722701</v>
+        <v>122720544</v>
       </c>
       <c r="B35" t="n">
-        <v>57494</v>
+        <v>78502</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4442,42 +4462,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581065</v>
+        <v>581116</v>
       </c>
       <c r="R35" t="n">
-        <v>7057691</v>
+        <v>7057570</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4506,7 +4521,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4516,7 +4531,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4543,10 +4558,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122722336</v>
+        <v>122721705</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4559,39 +4574,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581102</v>
+        <v>581182</v>
       </c>
       <c r="R36" t="n">
-        <v>7057625</v>
+        <v>7057497</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4623,7 +4633,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4633,12 +4643,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4653,22 +4658,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122720351</v>
+        <v>122720257</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4681,34 +4686,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581082</v>
+        <v>580942</v>
       </c>
       <c r="R37" t="n">
-        <v>7057561</v>
+        <v>7057618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4738,19 +4743,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4765,22 +4760,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122719531</v>
+        <v>122718678</v>
       </c>
       <c r="B38" t="n">
-        <v>79848</v>
+        <v>78502</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4793,21 +4788,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4817,10 +4812,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580913</v>
+        <v>581005</v>
       </c>
       <c r="R38" t="n">
-        <v>7057655</v>
+        <v>7057691</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4852,7 +4847,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4862,7 +4857,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4889,10 +4884,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122720366</v>
+        <v>122718748</v>
       </c>
       <c r="B39" t="n">
-        <v>78503</v>
+        <v>56688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4901,38 +4896,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581078</v>
+        <v>581004</v>
       </c>
       <c r="R39" t="n">
-        <v>7057568</v>
+        <v>7057692</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4989,22 +4989,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122722537</v>
+        <v>122722057</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5017,34 +5017,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581065</v>
+        <v>581149</v>
       </c>
       <c r="R40" t="n">
-        <v>7057691</v>
+        <v>7057577</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5076,7 +5081,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5086,7 +5091,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5101,22 +5111,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122721705</v>
+        <v>122719953</v>
       </c>
       <c r="B41" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5129,34 +5139,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581182</v>
+        <v>580942</v>
       </c>
       <c r="R41" t="n">
-        <v>7057497</v>
+        <v>7057618</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5186,19 +5196,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5213,22 +5213,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122719558</v>
+        <v>122719411</v>
       </c>
       <c r="B42" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5241,21 +5241,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5265,13 +5265,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580907</v>
+        <v>580961</v>
       </c>
       <c r="R42" t="n">
-        <v>7057652</v>
+        <v>7057655</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122722222</v>
+        <v>122720063</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5353,39 +5353,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581129</v>
+        <v>580986</v>
       </c>
       <c r="R43" t="n">
-        <v>7057634</v>
+        <v>7057585</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5417,7 +5412,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5427,12 +5422,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5459,10 +5449,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122719411</v>
+        <v>122719558</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5475,21 +5465,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5499,13 +5489,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580961</v>
+        <v>580907</v>
       </c>
       <c r="R44" t="n">
-        <v>7057655</v>
+        <v>7057652</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5571,10 +5561,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122718499</v>
+        <v>122719130</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5587,21 +5577,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5611,10 +5601,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580999</v>
+        <v>580985</v>
       </c>
       <c r="R45" t="n">
-        <v>7057695</v>
+        <v>7057694</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5646,7 +5636,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5656,7 +5646,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5683,10 +5673,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122720278</v>
+        <v>122722059</v>
       </c>
       <c r="B46" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5699,34 +5689,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580942</v>
+        <v>581149</v>
       </c>
       <c r="R46" t="n">
-        <v>7057618</v>
+        <v>7057571</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5756,9 +5746,24 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5773,22 +5778,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122720911</v>
+        <v>122720478</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5801,21 +5806,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5825,10 +5830,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581101</v>
+        <v>581116</v>
       </c>
       <c r="R47" t="n">
-        <v>7057443</v>
+        <v>7057570</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5860,7 +5865,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5870,12 +5875,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5890,22 +5890,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122721195</v>
+        <v>122721907</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5918,34 +5918,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581116</v>
+        <v>581134</v>
       </c>
       <c r="R48" t="n">
-        <v>7057434</v>
+        <v>7057504</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5975,9 +5980,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5992,22 +6007,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122718715</v>
+        <v>122719175</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6020,21 +6035,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6044,13 +6059,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581011</v>
+        <v>580984</v>
       </c>
       <c r="R49" t="n">
-        <v>7057695</v>
+        <v>7057676</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6079,7 +6094,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6089,7 +6104,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6104,19 +6119,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122719585</v>
+        <v>122722473</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -6152,14 +6167,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580901</v>
+        <v>581086</v>
       </c>
       <c r="R50" t="n">
-        <v>7057649</v>
+        <v>7057686</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6191,7 +6206,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6201,7 +6216,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6216,22 +6231,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122719696</v>
+        <v>122720366</v>
       </c>
       <c r="B51" t="n">
-        <v>78411</v>
+        <v>78503</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6244,34 +6259,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580901</v>
+        <v>581078</v>
       </c>
       <c r="R51" t="n">
-        <v>7057649</v>
+        <v>7057568</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6303,7 +6318,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6313,7 +6328,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6340,10 +6355,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122720528</v>
+        <v>122718715</v>
       </c>
       <c r="B52" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6356,21 +6371,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6380,10 +6395,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581073</v>
+        <v>581011</v>
       </c>
       <c r="R52" t="n">
-        <v>7057503</v>
+        <v>7057695</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6415,7 +6430,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6425,7 +6440,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6440,22 +6455,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122719953</v>
+        <v>122720577</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6468,34 +6483,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580942</v>
+        <v>581103</v>
       </c>
       <c r="R53" t="n">
-        <v>7057618</v>
+        <v>7057525</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6525,9 +6540,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6542,19 +6567,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122722568</v>
+        <v>122722537</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6594,10 +6619,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581036</v>
+        <v>581065</v>
       </c>
       <c r="R54" t="n">
-        <v>7057698</v>
+        <v>7057691</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6629,7 +6654,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6664,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6654,22 +6679,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122719250</v>
+        <v>122720361</v>
       </c>
       <c r="B55" t="n">
-        <v>90944</v>
+        <v>78502</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6682,21 +6707,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6706,13 +6731,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580977</v>
+        <v>581082</v>
       </c>
       <c r="R55" t="n">
-        <v>7057668</v>
+        <v>7057561</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6741,7 +6766,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6751,7 +6776,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6766,22 +6791,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122720361</v>
+        <v>122721195</v>
       </c>
       <c r="B56" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6794,21 +6819,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6818,13 +6843,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581082</v>
+        <v>581116</v>
       </c>
       <c r="R56" t="n">
-        <v>7057561</v>
+        <v>7057434</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6851,19 +6876,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6878,22 +6893,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122720063</v>
+        <v>122719828</v>
       </c>
       <c r="B57" t="n">
-        <v>78502</v>
+        <v>56688</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6902,38 +6917,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>580986</v>
+        <v>580901</v>
       </c>
       <c r="R57" t="n">
-        <v>7057585</v>
+        <v>7057649</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6965,7 +6985,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6975,7 +6995,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6990,22 +7010,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122719963</v>
+        <v>122718499</v>
       </c>
       <c r="B58" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7018,34 +7038,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580966</v>
+        <v>580999</v>
       </c>
       <c r="R58" t="n">
-        <v>7057594</v>
+        <v>7057695</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7077,7 +7097,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7087,7 +7107,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7102,22 +7122,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122721504</v>
+        <v>122719444</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7130,34 +7150,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581165</v>
+        <v>580956</v>
       </c>
       <c r="R59" t="n">
-        <v>7057471</v>
+        <v>7057671</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7187,19 +7207,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7214,22 +7224,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122720544</v>
+        <v>122720351</v>
       </c>
       <c r="B60" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7242,21 +7252,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7266,10 +7276,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581116</v>
+        <v>581082</v>
       </c>
       <c r="R60" t="n">
-        <v>7057570</v>
+        <v>7057561</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7301,7 +7311,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7311,7 +7321,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7338,10 +7348,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122722059</v>
+        <v>122719400</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7354,34 +7364,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581149</v>
+        <v>580956</v>
       </c>
       <c r="R61" t="n">
-        <v>7057571</v>
+        <v>7057671</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7411,24 +7421,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7443,19 +7438,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122719444</v>
+        <v>122721003</v>
       </c>
       <c r="B62" t="n">
         <v>78502</v>
@@ -7491,17 +7486,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580956</v>
+        <v>581112</v>
       </c>
       <c r="R62" t="n">
-        <v>7057671</v>
+        <v>7057450</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7528,9 +7523,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7545,19 +7550,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122720096</v>
+        <v>122718574</v>
       </c>
       <c r="B63" t="n">
         <v>79847</v>
@@ -7593,14 +7598,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580942</v>
+        <v>580996</v>
       </c>
       <c r="R63" t="n">
-        <v>7057618</v>
+        <v>7057711</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7630,11 +7635,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7643,31 +7658,16 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122721501</v>
+        <v>122721338</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,7 +721,7 @@
         <v>7057410</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721338</v>
+        <v>122721501</v>
       </c>
       <c r="B4" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,7 +950,7 @@
         <v>7057410</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122719696</v>
+        <v>122719585</v>
       </c>
       <c r="B5" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122719585</v>
+        <v>122719600</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580901</v>
+        <v>580956</v>
       </c>
       <c r="R6" t="n">
-        <v>7057649</v>
+        <v>7057671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,21 +1201,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1224,26 +1214,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122721655</v>
+        <v>122720546</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,37 +1261,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581182</v>
+        <v>581075</v>
       </c>
       <c r="R7" t="n">
-        <v>7057497</v>
+        <v>7057498</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122719358</v>
+        <v>122719953</v>
       </c>
       <c r="B8" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580961</v>
+        <v>580942</v>
       </c>
       <c r="R8" t="n">
-        <v>7057655</v>
+        <v>7057618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,19 +1440,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1457,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122719600</v>
+        <v>122719175</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,37 +1485,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580956</v>
+        <v>580984</v>
       </c>
       <c r="R9" t="n">
-        <v>7057671</v>
+        <v>7057676</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,11 +1542,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1550,41 +1565,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122721504</v>
+        <v>122719400</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581165</v>
+        <v>580956</v>
       </c>
       <c r="R10" t="n">
-        <v>7057471</v>
+        <v>7057671</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,19 +1654,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,22 +1671,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122721034</v>
+        <v>122720458</v>
       </c>
       <c r="B11" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581112</v>
+        <v>581098</v>
       </c>
       <c r="R11" t="n">
-        <v>7057450</v>
+        <v>7057575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122720457</v>
+        <v>122722537</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,39 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581081</v>
+        <v>581065</v>
       </c>
       <c r="R12" t="n">
-        <v>7057535</v>
+        <v>7057691</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,22 +1895,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122720096</v>
+        <v>122719444</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580942</v>
+        <v>580956</v>
       </c>
       <c r="R13" t="n">
-        <v>7057618</v>
+        <v>7057671</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,21 +1993,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2039,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122721690</v>
+        <v>122719461</v>
       </c>
       <c r="B14" t="n">
-        <v>91389</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2051,38 +2021,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581129</v>
+        <v>580912</v>
       </c>
       <c r="R14" t="n">
-        <v>7057525</v>
+        <v>7057652</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2114,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,22 +2109,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122721757</v>
+        <v>122720457</v>
       </c>
       <c r="B15" t="n">
-        <v>91235</v>
+        <v>57494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,34 +2137,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581120</v>
+        <v>581081</v>
       </c>
       <c r="R15" t="n">
-        <v>7057493</v>
+        <v>7057535</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2211,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122719442</v>
+        <v>122721757</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>91235</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,34 +2254,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580912</v>
+        <v>581120</v>
       </c>
       <c r="R16" t="n">
-        <v>7057652</v>
+        <v>7057493</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2323,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,22 +2338,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122720458</v>
+        <v>122719963</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,34 +2366,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581098</v>
+        <v>580966</v>
       </c>
       <c r="R17" t="n">
-        <v>7057575</v>
+        <v>7057594</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2450,7 +2425,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2435,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,10 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122721161</v>
+        <v>122721705</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,34 +2478,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581208</v>
+        <v>581182</v>
       </c>
       <c r="R18" t="n">
-        <v>7057450</v>
+        <v>7057497</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2537,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2547,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2587,22 +2562,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122720827</v>
+        <v>122721034</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,21 +2590,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2639,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581102</v>
+        <v>581112</v>
       </c>
       <c r="R19" t="n">
-        <v>7057553</v>
+        <v>7057450</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2674,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122721746</v>
+        <v>122721655</v>
       </c>
       <c r="B20" t="n">
-        <v>91389</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2723,25 +2698,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2751,13 +2726,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581131</v>
+        <v>581182</v>
       </c>
       <c r="R20" t="n">
-        <v>7057499</v>
+        <v>7057497</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2786,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2796,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2811,22 +2786,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122720546</v>
+        <v>122720544</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,39 +2814,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581075</v>
+        <v>581116</v>
       </c>
       <c r="R21" t="n">
-        <v>7057498</v>
+        <v>7057570</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,7 +2873,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,12 +2883,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2933,22 +2898,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122719963</v>
+        <v>122719531</v>
       </c>
       <c r="B22" t="n">
-        <v>78502</v>
+        <v>79848</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2961,34 +2926,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580966</v>
+        <v>580913</v>
       </c>
       <c r="R22" t="n">
-        <v>7057594</v>
+        <v>7057655</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3020,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +2995,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,12 +3010,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3174,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122719531</v>
+        <v>122720366</v>
       </c>
       <c r="B24" t="n">
-        <v>79848</v>
+        <v>78503</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3190,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3214,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580913</v>
+        <v>581078</v>
       </c>
       <c r="R24" t="n">
-        <v>7057655</v>
+        <v>7057568</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3249,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3259,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3274,19 +3239,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122720864</v>
+        <v>122718574</v>
       </c>
       <c r="B25" t="n">
         <v>79847</v>
@@ -3326,13 +3291,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581112</v>
+        <v>580996</v>
       </c>
       <c r="R25" t="n">
-        <v>7057450</v>
+        <v>7057711</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3361,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3371,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3386,22 +3351,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122722701</v>
+        <v>122721690</v>
       </c>
       <c r="B26" t="n">
-        <v>57494</v>
+        <v>91389</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3410,46 +3375,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581065</v>
+        <v>581129</v>
       </c>
       <c r="R26" t="n">
-        <v>7057691</v>
+        <v>7057525</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3478,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3488,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3503,22 +3463,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122722336</v>
+        <v>122719411</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3531,42 +3491,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581102</v>
+        <v>580961</v>
       </c>
       <c r="R27" t="n">
-        <v>7057625</v>
+        <v>7057655</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3595,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3605,12 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3625,19 +3575,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122722222</v>
+        <v>122722336</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3673,7 +3623,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3682,10 +3632,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581129</v>
+        <v>581102</v>
       </c>
       <c r="R28" t="n">
-        <v>7057634</v>
+        <v>7057625</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3717,7 +3667,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3727,12 +3677,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3759,10 +3709,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122720528</v>
+        <v>122722549</v>
       </c>
       <c r="B29" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3775,21 +3725,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3799,10 +3749,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581073</v>
+        <v>581043</v>
       </c>
       <c r="R29" t="n">
-        <v>7057503</v>
+        <v>7057689</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3834,7 +3784,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3844,7 +3794,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,22 +3809,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122719250</v>
+        <v>122719358</v>
       </c>
       <c r="B30" t="n">
-        <v>90944</v>
+        <v>78502</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3887,34 +3837,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580977</v>
+        <v>580961</v>
       </c>
       <c r="R30" t="n">
-        <v>7057668</v>
+        <v>7057655</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3946,7 +3896,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3956,7 +3906,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,22 +3921,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122720911</v>
+        <v>122718715</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3999,21 +3949,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4023,10 +3973,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581101</v>
+        <v>581011</v>
       </c>
       <c r="R31" t="n">
-        <v>7057443</v>
+        <v>7057695</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4058,7 +4008,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4068,12 +4018,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4088,22 +4033,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122722071</v>
+        <v>122720478</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4116,39 +4061,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581148</v>
+        <v>581116</v>
       </c>
       <c r="R32" t="n">
-        <v>7057575</v>
+        <v>7057570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4180,7 +4120,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4190,12 +4130,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4210,22 +4145,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122722549</v>
+        <v>122720063</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4238,21 +4173,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4262,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581043</v>
+        <v>580986</v>
       </c>
       <c r="R33" t="n">
-        <v>7057689</v>
+        <v>7057585</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4297,7 +4232,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4307,7 +4242,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4334,10 +4269,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122722568</v>
+        <v>122719130</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4350,21 +4285,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4374,10 +4309,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581036</v>
+        <v>580985</v>
       </c>
       <c r="R34" t="n">
-        <v>7057698</v>
+        <v>7057694</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4409,7 +4344,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4419,7 +4354,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4434,22 +4369,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122720544</v>
+        <v>122719558</v>
       </c>
       <c r="B35" t="n">
-        <v>78502</v>
+        <v>79848</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4462,34 +4397,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581116</v>
+        <v>580907</v>
       </c>
       <c r="R35" t="n">
-        <v>7057570</v>
+        <v>7057652</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4521,7 +4456,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4531,7 +4466,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4558,10 +4493,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122721705</v>
+        <v>122722568</v>
       </c>
       <c r="B36" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4574,21 +4509,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4598,10 +4533,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581182</v>
+        <v>581036</v>
       </c>
       <c r="R36" t="n">
-        <v>7057497</v>
+        <v>7057698</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4633,7 +4568,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4643,7 +4578,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4658,22 +4593,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122720257</v>
+        <v>122721746</v>
       </c>
       <c r="B37" t="n">
-        <v>78502</v>
+        <v>91389</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4682,38 +4617,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580942</v>
+        <v>581131</v>
       </c>
       <c r="R37" t="n">
-        <v>7057618</v>
+        <v>7057499</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4743,9 +4678,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4760,12 +4705,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4884,10 +4829,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122718748</v>
+        <v>122722701</v>
       </c>
       <c r="B39" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4896,31 +4841,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4929,13 +4874,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581004</v>
+        <v>581065</v>
       </c>
       <c r="R39" t="n">
-        <v>7057692</v>
+        <v>7057691</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4964,7 +4909,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4974,7 +4919,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4989,22 +4934,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122722057</v>
+        <v>122722473</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5017,39 +4962,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581149</v>
+        <v>581086</v>
       </c>
       <c r="R40" t="n">
-        <v>7057577</v>
+        <v>7057686</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5081,7 +5021,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5091,12 +5031,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5123,10 +5058,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122719953</v>
+        <v>122721504</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5139,34 +5074,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580942</v>
+        <v>581165</v>
       </c>
       <c r="R41" t="n">
-        <v>7057618</v>
+        <v>7057471</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5196,9 +5131,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5213,19 +5158,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122719411</v>
+        <v>122720827</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -5261,17 +5206,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580961</v>
+        <v>581102</v>
       </c>
       <c r="R42" t="n">
-        <v>7057655</v>
+        <v>7057553</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5300,7 +5245,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5310,7 +5255,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5337,10 +5282,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122720063</v>
+        <v>122722071</v>
       </c>
       <c r="B43" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5353,34 +5298,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580986</v>
+        <v>581148</v>
       </c>
       <c r="R43" t="n">
-        <v>7057585</v>
+        <v>7057575</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5412,7 +5362,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5422,7 +5372,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5449,10 +5404,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122719558</v>
+        <v>122722222</v>
       </c>
       <c r="B44" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5465,34 +5420,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580907</v>
+        <v>581129</v>
       </c>
       <c r="R44" t="n">
-        <v>7057652</v>
+        <v>7057634</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5524,7 +5484,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5534,7 +5494,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5549,22 +5514,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122719130</v>
+        <v>122720577</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>78411</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5577,21 +5542,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5601,10 +5566,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580985</v>
+        <v>581103</v>
       </c>
       <c r="R45" t="n">
-        <v>7057694</v>
+        <v>7057525</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5636,7 +5601,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5646,7 +5611,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5661,19 +5626,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122722059</v>
+        <v>122720911</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5713,10 +5678,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581149</v>
+        <v>581101</v>
       </c>
       <c r="R46" t="n">
-        <v>7057571</v>
+        <v>7057443</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5748,7 +5713,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5758,7 +5723,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5790,10 +5755,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122720478</v>
+        <v>122720278</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5806,34 +5771,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581116</v>
+        <v>580942</v>
       </c>
       <c r="R47" t="n">
-        <v>7057570</v>
+        <v>7057618</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5863,19 +5828,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5890,22 +5845,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122721907</v>
+        <v>122719250</v>
       </c>
       <c r="B48" t="n">
-        <v>57494</v>
+        <v>90944</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5918,39 +5873,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581134</v>
+        <v>580977</v>
       </c>
       <c r="R48" t="n">
-        <v>7057504</v>
+        <v>7057668</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5982,7 +5932,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5992,7 +5942,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6019,10 +5969,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122719175</v>
+        <v>122721003</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6035,21 +5985,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6059,13 +6009,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580984</v>
+        <v>581112</v>
       </c>
       <c r="R49" t="n">
-        <v>7057676</v>
+        <v>7057450</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6094,7 +6044,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6104,7 +6054,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6131,10 +6081,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122722473</v>
+        <v>122722057</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6147,34 +6097,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581086</v>
+        <v>581149</v>
       </c>
       <c r="R50" t="n">
-        <v>7057686</v>
+        <v>7057577</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6206,7 +6161,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6216,7 +6171,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6243,10 +6203,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122720366</v>
+        <v>122719696</v>
       </c>
       <c r="B51" t="n">
-        <v>78503</v>
+        <v>78411</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6259,34 +6219,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581078</v>
+        <v>580901</v>
       </c>
       <c r="R51" t="n">
-        <v>7057568</v>
+        <v>7057649</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6318,7 +6278,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6328,7 +6288,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6355,10 +6315,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122718715</v>
+        <v>122718748</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6367,38 +6327,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581011</v>
+        <v>581004</v>
       </c>
       <c r="R52" t="n">
-        <v>7057695</v>
+        <v>7057692</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6430,7 +6395,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6440,7 +6405,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6467,10 +6432,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122720577</v>
+        <v>122720351</v>
       </c>
       <c r="B53" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6483,21 +6448,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6507,10 +6472,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581103</v>
+        <v>581082</v>
       </c>
       <c r="R53" t="n">
-        <v>7057525</v>
+        <v>7057561</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6542,7 +6507,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6552,7 +6517,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6579,7 +6544,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122722537</v>
+        <v>122718499</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6619,10 +6584,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581065</v>
+        <v>580999</v>
       </c>
       <c r="R54" t="n">
-        <v>7057691</v>
+        <v>7057695</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6654,7 +6619,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6664,7 +6629,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6679,22 +6644,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122720361</v>
+        <v>122721907</v>
       </c>
       <c r="B55" t="n">
-        <v>78502</v>
+        <v>57494</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6707,37 +6672,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581082</v>
+        <v>581134</v>
       </c>
       <c r="R55" t="n">
-        <v>7057561</v>
+        <v>7057504</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6766,7 +6736,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6776,7 +6746,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6791,22 +6761,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122721195</v>
+        <v>122722059</v>
       </c>
       <c r="B56" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6819,21 +6789,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6843,10 +6813,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581116</v>
+        <v>581149</v>
       </c>
       <c r="R56" t="n">
-        <v>7057434</v>
+        <v>7057571</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6876,9 +6846,24 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6893,22 +6878,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122719828</v>
+        <v>122720361</v>
       </c>
       <c r="B57" t="n">
-        <v>56688</v>
+        <v>78502</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6917,46 +6902,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>580901</v>
+        <v>581082</v>
       </c>
       <c r="R57" t="n">
-        <v>7057649</v>
+        <v>7057561</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6985,7 +6965,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6995,7 +6975,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7022,10 +7002,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122718499</v>
+        <v>122721161</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7038,34 +7018,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580999</v>
+        <v>581208</v>
       </c>
       <c r="R58" t="n">
-        <v>7057695</v>
+        <v>7057450</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7097,7 +7077,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7107,7 +7087,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7122,22 +7102,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122719444</v>
+        <v>122720096</v>
       </c>
       <c r="B59" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7150,21 +7130,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7174,10 +7154,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580956</v>
+        <v>580942</v>
       </c>
       <c r="R59" t="n">
-        <v>7057671</v>
+        <v>7057618</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7220,6 +7200,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7236,10 +7231,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122720351</v>
+        <v>122721195</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7252,21 +7247,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7276,10 +7271,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581082</v>
+        <v>581116</v>
       </c>
       <c r="R60" t="n">
-        <v>7057561</v>
+        <v>7057434</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7309,19 +7304,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7336,22 +7321,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122719400</v>
+        <v>122719828</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7360,38 +7345,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580956</v>
+        <v>580901</v>
       </c>
       <c r="R61" t="n">
-        <v>7057671</v>
+        <v>7057649</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7421,9 +7411,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7438,22 +7438,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122721003</v>
+        <v>122720864</v>
       </c>
       <c r="B62" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7466,21 +7466,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7562,10 +7562,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122718574</v>
+        <v>122720528</v>
       </c>
       <c r="B63" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7578,21 +7578,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580996</v>
+        <v>581073</v>
       </c>
       <c r="R63" t="n">
-        <v>7057711</v>
+        <v>7057503</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7662,12 +7662,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122720458</v>
+        <v>122719461</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,34 +1699,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581098</v>
+        <v>580912</v>
       </c>
       <c r="R11" t="n">
-        <v>7057575</v>
+        <v>7057652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122722537</v>
+        <v>122720457</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,34 +1811,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581065</v>
+        <v>581081</v>
       </c>
       <c r="R12" t="n">
-        <v>7057691</v>
+        <v>7057535</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,22 +1900,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122719444</v>
+        <v>122721757</v>
       </c>
       <c r="B13" t="n">
-        <v>78502</v>
+        <v>91235</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,34 +1928,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580956</v>
+        <v>581120</v>
       </c>
       <c r="R13" t="n">
-        <v>7057671</v>
+        <v>7057493</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,9 +1985,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,22 +2012,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122719461</v>
+        <v>122720458</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,34 +2040,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580912</v>
+        <v>581098</v>
       </c>
       <c r="R14" t="n">
-        <v>7057652</v>
+        <v>7057575</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122720457</v>
+        <v>122722537</v>
       </c>
       <c r="B15" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,39 +2152,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581081</v>
+        <v>581065</v>
       </c>
       <c r="R15" t="n">
-        <v>7057535</v>
+        <v>7057691</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,22 +2236,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122721757</v>
+        <v>122719444</v>
       </c>
       <c r="B16" t="n">
-        <v>91235</v>
+        <v>78502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,34 +2264,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581120</v>
+        <v>580956</v>
       </c>
       <c r="R16" t="n">
-        <v>7057493</v>
+        <v>7057671</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,19 +2321,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,12 +2338,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122722701</v>
+        <v>122722473</v>
       </c>
       <c r="B39" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4845,42 +4845,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581065</v>
+        <v>581086</v>
       </c>
       <c r="R39" t="n">
-        <v>7057691</v>
+        <v>7057686</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4934,22 +4929,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122722473</v>
+        <v>122721504</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4962,21 +4957,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4986,10 +4981,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581086</v>
+        <v>581165</v>
       </c>
       <c r="R40" t="n">
-        <v>7057686</v>
+        <v>7057471</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5021,7 +5016,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5031,7 +5026,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5058,10 +5053,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122721504</v>
+        <v>122722701</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5074,37 +5069,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581165</v>
+        <v>581065</v>
       </c>
       <c r="R41" t="n">
-        <v>7057471</v>
+        <v>7057691</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5158,12 +5158,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122721907</v>
+        <v>122722059</v>
       </c>
       <c r="B55" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6672,16 +6672,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6690,21 +6690,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581134</v>
+        <v>581149</v>
       </c>
       <c r="R55" t="n">
-        <v>7057504</v>
+        <v>7057571</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6736,7 +6731,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6746,7 +6741,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6761,22 +6761,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122722059</v>
+        <v>122721907</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6789,16 +6789,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6807,16 +6807,21 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581149</v>
+        <v>581134</v>
       </c>
       <c r="R56" t="n">
-        <v>7057571</v>
+        <v>7057504</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6848,7 +6853,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6858,12 +6863,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6878,12 +6878,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122720546</v>
+        <v>122719953</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581075</v>
+        <v>580942</v>
       </c>
       <c r="R7" t="n">
-        <v>7057498</v>
+        <v>7057618</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,24 +1318,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,19 +1335,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122719953</v>
+        <v>122719175</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1403,17 +1383,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580942</v>
+        <v>580984</v>
       </c>
       <c r="R8" t="n">
-        <v>7057618</v>
+        <v>7057676</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,9 +1420,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,19 +1447,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122719175</v>
+        <v>122719400</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1505,17 +1495,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580984</v>
+        <v>580956</v>
       </c>
       <c r="R9" t="n">
-        <v>7057676</v>
+        <v>7057671</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,19 +1532,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,22 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122719400</v>
+        <v>122720546</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1577,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580956</v>
+        <v>581075</v>
       </c>
       <c r="R10" t="n">
-        <v>7057671</v>
+        <v>7057498</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,9 +1639,24 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,12 +1671,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2686,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122721655</v>
+        <v>122718574</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2702,21 +2702,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581182</v>
+        <v>580996</v>
       </c>
       <c r="R20" t="n">
-        <v>7057497</v>
+        <v>7057711</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,22 +2786,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122720544</v>
+        <v>122720366</v>
       </c>
       <c r="B21" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2814,21 +2814,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581116</v>
+        <v>581078</v>
       </c>
       <c r="R21" t="n">
-        <v>7057570</v>
+        <v>7057568</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2910,10 +2910,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122719531</v>
+        <v>122721655</v>
       </c>
       <c r="B22" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,13 +2950,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580913</v>
+        <v>581182</v>
       </c>
       <c r="R22" t="n">
-        <v>7057655</v>
+        <v>7057497</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,22 +3010,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122719214</v>
+        <v>122719531</v>
       </c>
       <c r="B23" t="n">
-        <v>56688</v>
+        <v>79848</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3034,46 +3034,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580978</v>
+        <v>580913</v>
       </c>
       <c r="R23" t="n">
-        <v>7057665</v>
+        <v>7057655</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3102,7 +3097,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3107,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,22 +3122,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122720366</v>
+        <v>122720544</v>
       </c>
       <c r="B24" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3150,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3174,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581078</v>
+        <v>581116</v>
       </c>
       <c r="R24" t="n">
-        <v>7057568</v>
+        <v>7057570</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,10 +3246,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122718574</v>
+        <v>122719214</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,41 +3258,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580996</v>
+        <v>580978</v>
       </c>
       <c r="R25" t="n">
-        <v>7057711</v>
+        <v>7057665</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3351,12 +3351,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4157,10 +4157,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122720063</v>
+        <v>122722568</v>
       </c>
       <c r="B33" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4173,21 +4173,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580986</v>
+        <v>581036</v>
       </c>
       <c r="R33" t="n">
-        <v>7057585</v>
+        <v>7057698</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4257,12 +4257,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4381,10 +4381,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122719558</v>
+        <v>122720063</v>
       </c>
       <c r="B35" t="n">
-        <v>79848</v>
+        <v>78502</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4397,34 +4397,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580907</v>
+        <v>580986</v>
       </c>
       <c r="R35" t="n">
-        <v>7057652</v>
+        <v>7057585</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4481,22 +4481,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122722568</v>
+        <v>122719558</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4509,34 +4509,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581036</v>
+        <v>580907</v>
       </c>
       <c r="R36" t="n">
-        <v>7057698</v>
+        <v>7057652</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4593,12 +4593,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5638,10 +5638,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122720911</v>
+        <v>122720278</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5654,34 +5654,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581101</v>
+        <v>580942</v>
       </c>
       <c r="R46" t="n">
-        <v>7057443</v>
+        <v>7057618</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5711,24 +5711,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5743,22 +5728,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122720278</v>
+        <v>122720911</v>
       </c>
       <c r="B47" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5771,34 +5756,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580942</v>
+        <v>581101</v>
       </c>
       <c r="R47" t="n">
-        <v>7057618</v>
+        <v>7057443</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5828,9 +5813,24 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5845,12 +5845,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -6656,10 +6656,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122722059</v>
+        <v>122721907</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6672,16 +6672,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6690,16 +6690,21 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581149</v>
+        <v>581134</v>
       </c>
       <c r="R55" t="n">
-        <v>7057571</v>
+        <v>7057504</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6731,7 +6736,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6741,12 +6746,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6761,22 +6761,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122721907</v>
+        <v>122722059</v>
       </c>
       <c r="B56" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6789,16 +6789,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6807,21 +6807,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581134</v>
+        <v>581149</v>
       </c>
       <c r="R56" t="n">
-        <v>7057504</v>
+        <v>7057571</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6853,7 +6848,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6863,7 +6858,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6878,12 +6878,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122719585</v>
+        <v>122719358</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580901</v>
+        <v>580961</v>
       </c>
       <c r="R5" t="n">
-        <v>7057649</v>
+        <v>7057655</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122719953</v>
+        <v>122719250</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580942</v>
+        <v>580977</v>
       </c>
       <c r="R7" t="n">
-        <v>7057618</v>
+        <v>7057668</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,9 +1318,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,22 +1345,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122719175</v>
+        <v>122719531</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1397,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580984</v>
+        <v>580913</v>
       </c>
       <c r="R8" t="n">
-        <v>7057676</v>
+        <v>7057655</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,22 +1457,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122719400</v>
+        <v>122719558</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580956</v>
+        <v>580907</v>
       </c>
       <c r="R9" t="n">
-        <v>7057671</v>
+        <v>7057652</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,9 +1542,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,22 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122720546</v>
+        <v>122719442</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,39 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581075</v>
+        <v>580912</v>
       </c>
       <c r="R10" t="n">
-        <v>7057498</v>
+        <v>7057652</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,12 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,22 +1681,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122719461</v>
+        <v>122720827</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,34 +1709,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580912</v>
+        <v>581102</v>
       </c>
       <c r="R11" t="n">
-        <v>7057652</v>
+        <v>7057553</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122720457</v>
+        <v>122721504</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,39 +1821,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581081</v>
+        <v>581165</v>
       </c>
       <c r="R12" t="n">
-        <v>7057535</v>
+        <v>7057471</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,22 +1905,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122721757</v>
+        <v>122720528</v>
       </c>
       <c r="B13" t="n">
-        <v>91235</v>
+        <v>78503</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,21 +1933,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581120</v>
+        <v>581073</v>
       </c>
       <c r="R13" t="n">
-        <v>7057493</v>
+        <v>7057503</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122720458</v>
+        <v>122718574</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,21 +2045,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581098</v>
+        <v>580996</v>
       </c>
       <c r="R14" t="n">
-        <v>7057575</v>
+        <v>7057711</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,22 +2129,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122722537</v>
+        <v>122722057</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,34 +2157,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581065</v>
+        <v>581149</v>
       </c>
       <c r="R15" t="n">
-        <v>7057691</v>
+        <v>7057577</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2231,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,22 +2251,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122719444</v>
+        <v>122720546</v>
       </c>
       <c r="B16" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,34 +2279,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580956</v>
+        <v>581075</v>
       </c>
       <c r="R16" t="n">
-        <v>7057671</v>
+        <v>7057498</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,9 +2341,24 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,19 +2373,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122719963</v>
+        <v>122720278</v>
       </c>
       <c r="B17" t="n">
         <v>78502</v>
@@ -2390,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580966</v>
+        <v>580942</v>
       </c>
       <c r="R17" t="n">
-        <v>7057594</v>
+        <v>7057618</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2423,19 +2458,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,22 +2475,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122721705</v>
+        <v>122721746</v>
       </c>
       <c r="B18" t="n">
-        <v>78502</v>
+        <v>91389</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2474,25 +2499,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581182</v>
+        <v>581131</v>
       </c>
       <c r="R18" t="n">
-        <v>7057497</v>
+        <v>7057499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2537,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2547,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,22 +2587,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122721034</v>
+        <v>122722568</v>
       </c>
       <c r="B19" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2590,21 +2615,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581112</v>
+        <v>581036</v>
       </c>
       <c r="R19" t="n">
-        <v>7057450</v>
+        <v>7057698</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2649,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,22 +2699,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122718574</v>
+        <v>122720544</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2702,21 +2727,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2726,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580996</v>
+        <v>581116</v>
       </c>
       <c r="R20" t="n">
-        <v>7057711</v>
+        <v>7057570</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2761,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2796,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,22 +2811,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122720366</v>
+        <v>122719585</v>
       </c>
       <c r="B21" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2814,34 +2839,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581078</v>
+        <v>580901</v>
       </c>
       <c r="R21" t="n">
-        <v>7057568</v>
+        <v>7057649</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2883,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2910,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122721655</v>
+        <v>122721161</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2926,37 +2951,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581182</v>
+        <v>581208</v>
       </c>
       <c r="R22" t="n">
-        <v>7057497</v>
+        <v>7057450</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2985,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,22 +3035,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122719531</v>
+        <v>122722336</v>
       </c>
       <c r="B23" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3038,34 +3063,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580913</v>
+        <v>581102</v>
       </c>
       <c r="R23" t="n">
-        <v>7057655</v>
+        <v>7057625</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3107,7 +3137,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3134,10 +3169,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122720544</v>
+        <v>122721195</v>
       </c>
       <c r="B24" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3150,21 +3185,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3177,7 +3212,7 @@
         <v>581116</v>
       </c>
       <c r="R24" t="n">
-        <v>7057570</v>
+        <v>7057434</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3207,19 +3242,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3234,22 +3259,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122719214</v>
+        <v>122720458</v>
       </c>
       <c r="B25" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3258,46 +3283,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580978</v>
+        <v>581098</v>
       </c>
       <c r="R25" t="n">
-        <v>7057665</v>
+        <v>7057575</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3326,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,10 +3383,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122721690</v>
+        <v>122719175</v>
       </c>
       <c r="B26" t="n">
-        <v>91389</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,25 +3395,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,13 +3423,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581129</v>
+        <v>580984</v>
       </c>
       <c r="R26" t="n">
-        <v>7057525</v>
+        <v>7057676</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3438,7 +3458,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3468,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3463,22 +3483,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122719411</v>
+        <v>122720096</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,21 +3511,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,13 +3535,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580961</v>
+        <v>580942</v>
       </c>
       <c r="R27" t="n">
-        <v>7057655</v>
+        <v>7057618</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3548,21 +3568,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3571,26 +3581,41 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122722336</v>
+        <v>122720457</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,16 +3628,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3632,10 +3657,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581102</v>
+        <v>581081</v>
       </c>
       <c r="R28" t="n">
-        <v>7057625</v>
+        <v>7057535</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3667,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3677,12 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3697,12 +3717,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3821,10 +3841,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122719358</v>
+        <v>122722701</v>
       </c>
       <c r="B30" t="n">
-        <v>78502</v>
+        <v>57494</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3837,37 +3857,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580961</v>
+        <v>581065</v>
       </c>
       <c r="R30" t="n">
-        <v>7057655</v>
+        <v>7057691</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3896,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3906,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3933,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122718715</v>
+        <v>122722071</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3949,34 +3974,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581011</v>
+        <v>581148</v>
       </c>
       <c r="R31" t="n">
-        <v>7057695</v>
+        <v>7057575</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4008,7 +4038,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4018,7 +4048,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4045,10 +4080,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122720478</v>
+        <v>122721034</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4061,21 +4096,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4085,10 +4120,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581116</v>
+        <v>581112</v>
       </c>
       <c r="R32" t="n">
-        <v>7057570</v>
+        <v>7057450</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4120,7 +4155,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4130,7 +4165,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4157,10 +4192,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122722568</v>
+        <v>122719696</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4173,34 +4208,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581036</v>
+        <v>580901</v>
       </c>
       <c r="R33" t="n">
-        <v>7057698</v>
+        <v>7057649</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,7 +4267,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4242,7 +4277,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4257,22 +4292,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122719130</v>
+        <v>122721757</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>91235</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4285,21 +4320,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4309,10 +4344,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580985</v>
+        <v>581120</v>
       </c>
       <c r="R34" t="n">
-        <v>7057694</v>
+        <v>7057493</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4344,7 +4379,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4354,7 +4389,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4369,22 +4404,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122720063</v>
+        <v>122722222</v>
       </c>
       <c r="B35" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4397,34 +4432,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580986</v>
+        <v>581129</v>
       </c>
       <c r="R35" t="n">
-        <v>7057585</v>
+        <v>7057634</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,7 +4496,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4466,7 +4506,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4493,10 +4538,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122719558</v>
+        <v>122720361</v>
       </c>
       <c r="B36" t="n">
-        <v>79848</v>
+        <v>78502</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4509,37 +4554,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580907</v>
+        <v>581082</v>
       </c>
       <c r="R36" t="n">
-        <v>7057652</v>
+        <v>7057561</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4568,7 +4613,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4578,7 +4623,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4605,10 +4650,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122721746</v>
+        <v>122720063</v>
       </c>
       <c r="B37" t="n">
-        <v>91389</v>
+        <v>78502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4617,25 +4662,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4645,10 +4690,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581131</v>
+        <v>580986</v>
       </c>
       <c r="R37" t="n">
-        <v>7057499</v>
+        <v>7057585</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4680,7 +4725,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4690,7 +4735,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4705,22 +4750,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122718678</v>
+        <v>122720351</v>
       </c>
       <c r="B38" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4733,21 +4778,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4757,10 +4802,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581005</v>
+        <v>581082</v>
       </c>
       <c r="R38" t="n">
-        <v>7057691</v>
+        <v>7057561</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4792,7 +4837,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4802,7 +4847,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4817,19 +4862,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122722473</v>
+        <v>122719411</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4865,17 +4910,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581086</v>
+        <v>580961</v>
       </c>
       <c r="R39" t="n">
-        <v>7057686</v>
+        <v>7057655</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4904,7 +4949,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4914,7 +4959,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4929,22 +4974,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122721504</v>
+        <v>122720577</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>78411</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4957,21 +5002,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4981,10 +5026,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581165</v>
+        <v>581103</v>
       </c>
       <c r="R40" t="n">
-        <v>7057471</v>
+        <v>7057525</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5016,7 +5061,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5026,7 +5071,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5041,22 +5086,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122722701</v>
+        <v>122718715</v>
       </c>
       <c r="B41" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5069,42 +5114,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581065</v>
+        <v>581011</v>
       </c>
       <c r="R41" t="n">
-        <v>7057691</v>
+        <v>7057695</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5133,7 +5173,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5143,7 +5183,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5158,22 +5198,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122720827</v>
+        <v>122721705</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5186,21 +5226,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5210,10 +5250,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581102</v>
+        <v>581182</v>
       </c>
       <c r="R42" t="n">
-        <v>7057553</v>
+        <v>7057497</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5245,7 +5285,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5255,7 +5295,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5282,10 +5322,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122722071</v>
+        <v>122721003</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5298,42 +5338,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581148</v>
+        <v>581112</v>
       </c>
       <c r="R43" t="n">
-        <v>7057575</v>
+        <v>7057450</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5362,7 +5397,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5372,12 +5407,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5392,22 +5422,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122722222</v>
+        <v>122722473</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5420,39 +5450,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581129</v>
+        <v>581086</v>
       </c>
       <c r="R44" t="n">
-        <v>7057634</v>
+        <v>7057686</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5484,7 +5509,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5494,12 +5519,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5526,10 +5546,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122720577</v>
+        <v>122720911</v>
       </c>
       <c r="B45" t="n">
-        <v>78411</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5542,21 +5562,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5566,10 +5586,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581103</v>
+        <v>581101</v>
       </c>
       <c r="R45" t="n">
-        <v>7057525</v>
+        <v>7057443</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5601,7 +5621,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5611,7 +5631,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5626,22 +5651,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122720278</v>
+        <v>122719214</v>
       </c>
       <c r="B46" t="n">
-        <v>78502</v>
+        <v>56688</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5650,41 +5675,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580942</v>
+        <v>580978</v>
       </c>
       <c r="R46" t="n">
-        <v>7057618</v>
+        <v>7057665</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5711,9 +5741,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5728,22 +5768,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122720911</v>
+        <v>122720366</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5756,21 +5796,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5780,10 +5820,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581101</v>
+        <v>581078</v>
       </c>
       <c r="R47" t="n">
-        <v>7057443</v>
+        <v>7057568</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5815,7 +5855,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5825,12 +5865,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5845,22 +5880,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122719250</v>
+        <v>122721690</v>
       </c>
       <c r="B48" t="n">
-        <v>90944</v>
+        <v>91389</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5869,25 +5904,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5897,10 +5932,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580977</v>
+        <v>581129</v>
       </c>
       <c r="R48" t="n">
-        <v>7057668</v>
+        <v>7057525</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5932,7 +5967,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5942,7 +5977,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5969,10 +6004,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122721003</v>
+        <v>122722059</v>
       </c>
       <c r="B49" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5985,21 +6020,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6009,13 +6044,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581112</v>
+        <v>581149</v>
       </c>
       <c r="R49" t="n">
-        <v>7057450</v>
+        <v>7057571</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6044,7 +6079,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6054,7 +6089,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6069,22 +6109,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122722057</v>
+        <v>122722537</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6097,39 +6137,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581149</v>
+        <v>581065</v>
       </c>
       <c r="R50" t="n">
-        <v>7057577</v>
+        <v>7057691</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6161,7 +6196,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6171,12 +6206,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6191,22 +6221,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122719696</v>
+        <v>122721907</v>
       </c>
       <c r="B51" t="n">
-        <v>78411</v>
+        <v>57494</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6219,34 +6249,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580901</v>
+        <v>581134</v>
       </c>
       <c r="R51" t="n">
-        <v>7057649</v>
+        <v>7057504</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6278,7 +6313,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6288,7 +6323,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6303,22 +6338,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122718748</v>
+        <v>122719444</v>
       </c>
       <c r="B52" t="n">
-        <v>56688</v>
+        <v>78502</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6327,43 +6362,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581004</v>
+        <v>580956</v>
       </c>
       <c r="R52" t="n">
-        <v>7057692</v>
+        <v>7057671</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6393,19 +6423,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6420,19 +6440,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122720351</v>
+        <v>122720478</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -6472,10 +6492,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581082</v>
+        <v>581116</v>
       </c>
       <c r="R53" t="n">
-        <v>7057561</v>
+        <v>7057570</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6507,7 +6527,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6517,7 +6537,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6544,7 +6564,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122718499</v>
+        <v>122719400</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6580,14 +6600,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580999</v>
+        <v>580956</v>
       </c>
       <c r="R54" t="n">
-        <v>7057695</v>
+        <v>7057671</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6617,19 +6637,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:58</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6644,22 +6654,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122721907</v>
+        <v>122719953</v>
       </c>
       <c r="B55" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6672,39 +6682,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581134</v>
+        <v>580942</v>
       </c>
       <c r="R55" t="n">
-        <v>7057504</v>
+        <v>7057618</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6734,19 +6739,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6761,22 +6756,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122722059</v>
+        <v>122721655</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6789,21 +6784,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6813,13 +6808,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581149</v>
+        <v>581182</v>
       </c>
       <c r="R56" t="n">
-        <v>7057571</v>
+        <v>7057497</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6848,7 +6843,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6858,12 +6853,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6878,22 +6868,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122720361</v>
+        <v>122719130</v>
       </c>
       <c r="B57" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6906,21 +6896,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6930,13 +6920,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581082</v>
+        <v>580985</v>
       </c>
       <c r="R57" t="n">
-        <v>7057561</v>
+        <v>7057694</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6965,7 +6955,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6975,7 +6965,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6990,22 +6980,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122721161</v>
+        <v>122719828</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7014,38 +7004,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581208</v>
+        <v>580901</v>
       </c>
       <c r="R58" t="n">
-        <v>7057450</v>
+        <v>7057649</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7077,7 +7072,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7087,7 +7082,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7102,22 +7097,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122720096</v>
+        <v>122719963</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7130,21 +7125,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7154,10 +7149,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580942</v>
+        <v>580966</v>
       </c>
       <c r="R59" t="n">
-        <v>7057618</v>
+        <v>7057594</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7187,11 +7182,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7200,41 +7205,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122721195</v>
+        <v>122718678</v>
       </c>
       <c r="B60" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7247,21 +7237,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7271,10 +7261,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581116</v>
+        <v>581005</v>
       </c>
       <c r="R60" t="n">
-        <v>7057434</v>
+        <v>7057691</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7304,9 +7294,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7321,22 +7321,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122719828</v>
+        <v>122718499</v>
       </c>
       <c r="B61" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7345,43 +7345,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580901</v>
+        <v>580999</v>
       </c>
       <c r="R61" t="n">
-        <v>7057649</v>
+        <v>7057695</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7413,7 +7408,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7423,7 +7418,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7438,12 +7433,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7562,10 +7557,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122720528</v>
+        <v>122718748</v>
       </c>
       <c r="B63" t="n">
-        <v>78503</v>
+        <v>56688</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7574,38 +7569,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581073</v>
+        <v>581004</v>
       </c>
       <c r="R63" t="n">
-        <v>7057503</v>
+        <v>7057692</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7662,12 +7662,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -5546,10 +5546,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122720911</v>
+        <v>122720366</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5586,10 +5586,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581101</v>
+        <v>581078</v>
       </c>
       <c r="R45" t="n">
-        <v>7057443</v>
+        <v>7057568</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5631,12 +5631,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5651,22 +5646,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122719214</v>
+        <v>122720911</v>
       </c>
       <c r="B46" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5675,46 +5670,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580978</v>
+        <v>581101</v>
       </c>
       <c r="R46" t="n">
-        <v>7057665</v>
+        <v>7057443</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5743,7 +5733,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5753,7 +5743,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5768,22 +5763,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122720366</v>
+        <v>122719214</v>
       </c>
       <c r="B47" t="n">
-        <v>78503</v>
+        <v>56688</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5792,41 +5787,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581078</v>
+        <v>580978</v>
       </c>
       <c r="R47" t="n">
-        <v>7057568</v>
+        <v>7057665</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6666,10 +6666,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122719953</v>
+        <v>122719963</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6682,21 +6682,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580942</v>
+        <v>580966</v>
       </c>
       <c r="R55" t="n">
-        <v>7057618</v>
+        <v>7057594</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6739,9 +6739,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6756,22 +6766,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122721655</v>
+        <v>122718678</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6784,21 +6794,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6808,13 +6818,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581182</v>
+        <v>581005</v>
       </c>
       <c r="R56" t="n">
-        <v>7057497</v>
+        <v>7057691</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6843,7 +6853,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6853,7 +6863,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6868,22 +6878,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122719130</v>
+        <v>122719953</v>
       </c>
       <c r="B57" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6896,34 +6906,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>580985</v>
+        <v>580942</v>
       </c>
       <c r="R57" t="n">
-        <v>7057694</v>
+        <v>7057618</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6953,19 +6963,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6980,22 +6980,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122719828</v>
+        <v>122721655</v>
       </c>
       <c r="B58" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7004,46 +7004,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580901</v>
+        <v>581182</v>
       </c>
       <c r="R58" t="n">
-        <v>7057649</v>
+        <v>7057497</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7072,7 +7067,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7082,7 +7077,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7109,10 +7104,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122719963</v>
+        <v>122719828</v>
       </c>
       <c r="B59" t="n">
-        <v>78502</v>
+        <v>56688</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7121,38 +7116,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580966</v>
+        <v>580901</v>
       </c>
       <c r="R59" t="n">
-        <v>7057594</v>
+        <v>7057649</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7221,10 +7221,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122718678</v>
+        <v>122719130</v>
       </c>
       <c r="B60" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7237,21 +7237,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7261,10 +7261,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581005</v>
+        <v>580985</v>
       </c>
       <c r="R60" t="n">
-        <v>7057691</v>
+        <v>7057694</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7333,10 +7333,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122718499</v>
+        <v>122720864</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7349,21 +7349,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7373,13 +7373,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580999</v>
+        <v>581112</v>
       </c>
       <c r="R61" t="n">
-        <v>7057695</v>
+        <v>7057450</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7433,22 +7433,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122720864</v>
+        <v>122718748</v>
       </c>
       <c r="B62" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7457,41 +7457,46 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581112</v>
+        <v>581004</v>
       </c>
       <c r="R62" t="n">
-        <v>7057450</v>
+        <v>7057692</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7520,7 +7525,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7530,7 +7535,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7545,22 +7550,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122718748</v>
+        <v>122718499</v>
       </c>
       <c r="B63" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7569,43 +7574,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581004</v>
+        <v>580999</v>
       </c>
       <c r="R63" t="n">
-        <v>7057692</v>
+        <v>7057695</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -5892,10 +5892,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122721690</v>
+        <v>122722059</v>
       </c>
       <c r="B48" t="n">
-        <v>91389</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5904,25 +5904,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581129</v>
+        <v>581149</v>
       </c>
       <c r="R48" t="n">
-        <v>7057525</v>
+        <v>7057571</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5977,7 +5977,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5992,22 +5997,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122722059</v>
+        <v>122721690</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>91389</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6016,25 +6021,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6044,10 +6049,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581149</v>
+        <v>581129</v>
       </c>
       <c r="R49" t="n">
-        <v>7057571</v>
+        <v>7057525</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6079,7 +6084,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6089,12 +6094,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6109,22 +6109,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122722537</v>
+        <v>122721907</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6137,34 +6137,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581065</v>
+        <v>581134</v>
       </c>
       <c r="R50" t="n">
-        <v>7057691</v>
+        <v>7057504</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6196,7 +6201,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6206,7 +6211,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6221,22 +6226,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122721907</v>
+        <v>122722537</v>
       </c>
       <c r="B51" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6249,39 +6254,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581134</v>
+        <v>581065</v>
       </c>
       <c r="R51" t="n">
-        <v>7057504</v>
+        <v>7057691</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6338,12 +6338,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122721338</v>
+        <v>122721113</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581145</v>
+        <v>581208</v>
       </c>
       <c r="R2" t="n">
-        <v>7057410</v>
+        <v>7057415</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721113</v>
+        <v>122721501</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581208</v>
+        <v>581145</v>
       </c>
       <c r="R3" t="n">
-        <v>7057415</v>
+        <v>7057410</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721501</v>
+        <v>122721338</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,7 +950,7 @@
         <v>7057410</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122719358</v>
+        <v>122721003</v>
       </c>
       <c r="B5" t="n">
         <v>78502</v>
@@ -1052,17 +1052,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580961</v>
+        <v>581112</v>
       </c>
       <c r="R5" t="n">
-        <v>7057655</v>
+        <v>7057450</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122719600</v>
+        <v>122719585</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580956</v>
+        <v>580901</v>
       </c>
       <c r="R6" t="n">
-        <v>7057671</v>
+        <v>7057649</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,11 +1201,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1214,41 +1224,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122719250</v>
+        <v>122719175</v>
       </c>
       <c r="B7" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,13 +1280,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580977</v>
+        <v>580984</v>
       </c>
       <c r="R7" t="n">
-        <v>7057668</v>
+        <v>7057676</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,22 +1340,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122719531</v>
+        <v>122720063</v>
       </c>
       <c r="B8" t="n">
-        <v>79848</v>
+        <v>78502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580913</v>
+        <v>580986</v>
       </c>
       <c r="R8" t="n">
-        <v>7057655</v>
+        <v>7057585</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122719558</v>
+        <v>122718748</v>
       </c>
       <c r="B9" t="n">
-        <v>79848</v>
+        <v>56688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,38 +1476,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580907</v>
+        <v>581004</v>
       </c>
       <c r="R9" t="n">
-        <v>7057652</v>
+        <v>7057692</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,22 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122719442</v>
+        <v>122720911</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580912</v>
+        <v>581101</v>
       </c>
       <c r="R10" t="n">
-        <v>7057652</v>
+        <v>7057443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,22 +1686,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122720827</v>
+        <v>122722336</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,24 +1714,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
@@ -1736,7 +1746,7 @@
         <v>581102</v>
       </c>
       <c r="R11" t="n">
-        <v>7057553</v>
+        <v>7057625</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1788,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,22 +1808,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122721504</v>
+        <v>122720528</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581165</v>
+        <v>581073</v>
       </c>
       <c r="R12" t="n">
-        <v>7057471</v>
+        <v>7057503</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1880,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,22 +1920,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122720528</v>
+        <v>122720544</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,21 +1948,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581073</v>
+        <v>581116</v>
       </c>
       <c r="R13" t="n">
-        <v>7057503</v>
+        <v>7057570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,22 +2032,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122718574</v>
+        <v>122719828</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,38 +2056,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580996</v>
+        <v>580901</v>
       </c>
       <c r="R14" t="n">
-        <v>7057711</v>
+        <v>7057649</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,22 +2149,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122722057</v>
+        <v>122718574</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,39 +2177,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581149</v>
+        <v>580996</v>
       </c>
       <c r="R15" t="n">
-        <v>7057577</v>
+        <v>7057711</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,12 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2273,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122720546</v>
+        <v>122719250</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,39 +2289,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581075</v>
+        <v>580977</v>
       </c>
       <c r="R16" t="n">
-        <v>7057498</v>
+        <v>7057668</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,7 +2348,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,12 +2358,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122720278</v>
+        <v>122719442</v>
       </c>
       <c r="B17" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,21 +2401,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580942</v>
+        <v>580912</v>
       </c>
       <c r="R17" t="n">
-        <v>7057618</v>
+        <v>7057652</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,9 +2458,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2475,22 +2485,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122721746</v>
+        <v>122721705</v>
       </c>
       <c r="B18" t="n">
-        <v>91389</v>
+        <v>78502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,25 +2509,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2527,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581131</v>
+        <v>581182</v>
       </c>
       <c r="R18" t="n">
-        <v>7057499</v>
+        <v>7057497</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2587,22 +2597,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122722568</v>
+        <v>122718715</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,21 +2625,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2639,10 +2649,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581036</v>
+        <v>581011</v>
       </c>
       <c r="R19" t="n">
-        <v>7057698</v>
+        <v>7057695</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2674,7 +2684,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2694,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2699,22 +2709,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122720544</v>
+        <v>122721034</v>
       </c>
       <c r="B20" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,21 +2737,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2751,10 +2761,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581116</v>
+        <v>581112</v>
       </c>
       <c r="R20" t="n">
-        <v>7057570</v>
+        <v>7057450</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2786,7 +2796,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2796,7 +2806,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,10 +2833,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122719585</v>
+        <v>122720257</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,21 +2849,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2863,10 +2873,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580901</v>
+        <v>580942</v>
       </c>
       <c r="R21" t="n">
-        <v>7057649</v>
+        <v>7057618</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2896,19 +2906,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2923,22 +2923,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122721161</v>
+        <v>122720351</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,34 +2951,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581208</v>
+        <v>581082</v>
       </c>
       <c r="R22" t="n">
-        <v>7057450</v>
+        <v>7057561</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,22 +3035,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122722336</v>
+        <v>122720096</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,39 +3063,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581102</v>
+        <v>580942</v>
       </c>
       <c r="R23" t="n">
-        <v>7057625</v>
+        <v>7057618</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3125,26 +3120,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:11</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3153,23 +3133,38 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122721195</v>
+        <v>122721161</v>
       </c>
       <c r="B24" t="n">
         <v>79847</v>
@@ -3205,14 +3200,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581116</v>
+        <v>581208</v>
       </c>
       <c r="R24" t="n">
-        <v>7057434</v>
+        <v>7057450</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3242,9 +3237,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,19 +3264,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122720458</v>
+        <v>122719953</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3307,14 +3312,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581098</v>
+        <v>580942</v>
       </c>
       <c r="R25" t="n">
-        <v>7057575</v>
+        <v>7057618</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,19 +3349,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,19 +3366,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122719175</v>
+        <v>122720827</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3423,13 +3418,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580984</v>
+        <v>581102</v>
       </c>
       <c r="R26" t="n">
-        <v>7057676</v>
+        <v>7057553</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3458,7 +3453,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3468,7 +3463,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,10 +3490,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122720096</v>
+        <v>122719358</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3511,21 +3506,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3535,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580942</v>
+        <v>580961</v>
       </c>
       <c r="R27" t="n">
-        <v>7057618</v>
+        <v>7057655</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3568,11 +3563,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3581,41 +3586,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122720457</v>
+        <v>122718499</v>
       </c>
       <c r="B28" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3628,39 +3618,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581081</v>
+        <v>580999</v>
       </c>
       <c r="R28" t="n">
-        <v>7057535</v>
+        <v>7057695</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3692,7 +3677,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3687,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3717,19 +3702,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122722549</v>
+        <v>122722568</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3769,10 +3754,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581043</v>
+        <v>581036</v>
       </c>
       <c r="R29" t="n">
-        <v>7057689</v>
+        <v>7057698</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3804,7 +3789,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3814,7 +3799,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3829,22 +3814,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122722701</v>
+        <v>122719214</v>
       </c>
       <c r="B30" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3853,31 +3838,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3886,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581065</v>
+        <v>580978</v>
       </c>
       <c r="R30" t="n">
-        <v>7057691</v>
+        <v>7057665</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3921,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122722071</v>
+        <v>122719130</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,39 +3959,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581148</v>
+        <v>580985</v>
       </c>
       <c r="R31" t="n">
-        <v>7057575</v>
+        <v>7057694</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4038,7 +4018,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4048,12 +4028,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4080,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122721034</v>
+        <v>122719600</v>
       </c>
       <c r="B32" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4096,34 +4071,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581112</v>
+        <v>580956</v>
       </c>
       <c r="R32" t="n">
-        <v>7057450</v>
+        <v>7057671</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4153,21 +4128,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4176,26 +4141,41 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122719696</v>
+        <v>122722473</v>
       </c>
       <c r="B33" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4208,34 +4188,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580901</v>
+        <v>581086</v>
       </c>
       <c r="R33" t="n">
-        <v>7057649</v>
+        <v>7057686</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4267,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4277,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4292,22 +4272,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122721757</v>
+        <v>122721195</v>
       </c>
       <c r="B34" t="n">
-        <v>91235</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4320,21 +4300,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4344,10 +4324,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581120</v>
+        <v>581116</v>
       </c>
       <c r="R34" t="n">
-        <v>7057493</v>
+        <v>7057434</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4377,19 +4357,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,22 +4374,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122722222</v>
+        <v>122720385</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4432,39 +4402,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581129</v>
+        <v>581098</v>
       </c>
       <c r="R35" t="n">
-        <v>7057634</v>
+        <v>7057575</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4496,7 +4461,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4506,12 +4471,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4526,22 +4486,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122720361</v>
+        <v>122719411</v>
       </c>
       <c r="B36" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4554,34 +4514,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581082</v>
+        <v>580961</v>
       </c>
       <c r="R36" t="n">
-        <v>7057561</v>
+        <v>7057655</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4613,7 +4573,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4623,7 +4583,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4650,10 +4610,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122720063</v>
+        <v>122722537</v>
       </c>
       <c r="B37" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4666,21 +4626,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4690,10 +4650,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580986</v>
+        <v>581065</v>
       </c>
       <c r="R37" t="n">
-        <v>7057585</v>
+        <v>7057691</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4725,7 +4685,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4735,7 +4695,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4750,22 +4710,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122720351</v>
+        <v>122720361</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4778,21 +4738,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4808,7 +4768,7 @@
         <v>7057561</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4837,7 +4797,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4847,7 +4807,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4874,10 +4834,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122719411</v>
+        <v>122719531</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4890,37 +4850,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580961</v>
+        <v>580913</v>
       </c>
       <c r="R39" t="n">
         <v>7057655</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4949,7 +4909,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4959,7 +4919,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4974,22 +4934,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122720577</v>
+        <v>122722059</v>
       </c>
       <c r="B40" t="n">
-        <v>78411</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5002,21 +4962,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5026,10 +4986,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581103</v>
+        <v>581149</v>
       </c>
       <c r="R40" t="n">
-        <v>7057525</v>
+        <v>7057571</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5061,7 +5021,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5071,7 +5031,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5086,22 +5051,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122718715</v>
+        <v>122720457</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5114,34 +5079,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581011</v>
+        <v>581081</v>
       </c>
       <c r="R41" t="n">
-        <v>7057695</v>
+        <v>7057535</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5173,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5183,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5198,22 +5168,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122721705</v>
+        <v>122719696</v>
       </c>
       <c r="B42" t="n">
-        <v>78502</v>
+        <v>78411</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5226,34 +5196,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581182</v>
+        <v>580901</v>
       </c>
       <c r="R42" t="n">
-        <v>7057497</v>
+        <v>7057649</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5285,7 +5255,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5295,7 +5265,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5322,10 +5292,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122721003</v>
+        <v>122720478</v>
       </c>
       <c r="B43" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5338,21 +5308,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5362,13 +5332,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581112</v>
+        <v>581116</v>
       </c>
       <c r="R43" t="n">
-        <v>7057450</v>
+        <v>7057570</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5397,7 +5367,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5407,7 +5377,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5434,10 +5404,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122722473</v>
+        <v>122722222</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5450,34 +5420,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581086</v>
+        <v>581129</v>
       </c>
       <c r="R44" t="n">
-        <v>7057686</v>
+        <v>7057634</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5509,7 +5484,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5519,7 +5494,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5546,10 +5526,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122720366</v>
+        <v>122719400</v>
       </c>
       <c r="B45" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5562,34 +5542,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581078</v>
+        <v>580956</v>
       </c>
       <c r="R45" t="n">
-        <v>7057568</v>
+        <v>7057671</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5619,19 +5599,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5646,22 +5616,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122720911</v>
+        <v>122722701</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5674,16 +5644,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5692,19 +5662,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581101</v>
+        <v>581065</v>
       </c>
       <c r="R46" t="n">
-        <v>7057443</v>
+        <v>7057691</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5733,7 +5708,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5743,12 +5718,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5763,22 +5733,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122719214</v>
+        <v>122722071</v>
       </c>
       <c r="B47" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5787,31 +5757,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5820,13 +5790,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580978</v>
+        <v>581148</v>
       </c>
       <c r="R47" t="n">
-        <v>7057665</v>
+        <v>7057575</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5855,7 +5825,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5865,7 +5835,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5880,22 +5855,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122722059</v>
+        <v>122721504</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5908,21 +5883,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5932,10 +5907,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581149</v>
+        <v>581165</v>
       </c>
       <c r="R48" t="n">
-        <v>7057571</v>
+        <v>7057471</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5967,7 +5942,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5977,12 +5952,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5997,22 +5967,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122721690</v>
+        <v>122719444</v>
       </c>
       <c r="B49" t="n">
-        <v>91389</v>
+        <v>78502</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6021,38 +5991,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581129</v>
+        <v>580956</v>
       </c>
       <c r="R49" t="n">
-        <v>7057525</v>
+        <v>7057671</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6082,19 +6052,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6109,22 +6069,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122721907</v>
+        <v>122718678</v>
       </c>
       <c r="B50" t="n">
-        <v>57494</v>
+        <v>78502</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6137,39 +6097,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581134</v>
+        <v>581005</v>
       </c>
       <c r="R50" t="n">
-        <v>7057504</v>
+        <v>7057691</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6201,7 +6156,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6211,7 +6166,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6238,10 +6193,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122722537</v>
+        <v>122719558</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6254,34 +6209,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581065</v>
+        <v>580907</v>
       </c>
       <c r="R51" t="n">
-        <v>7057691</v>
+        <v>7057652</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6313,7 +6268,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6323,7 +6278,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6350,10 +6305,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122719444</v>
+        <v>122720366</v>
       </c>
       <c r="B52" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6366,34 +6321,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580956</v>
+        <v>581078</v>
       </c>
       <c r="R52" t="n">
-        <v>7057671</v>
+        <v>7057568</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6423,9 +6378,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6440,22 +6405,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122720478</v>
+        <v>122722057</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6468,34 +6433,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581116</v>
+        <v>581149</v>
       </c>
       <c r="R53" t="n">
-        <v>7057570</v>
+        <v>7057577</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6527,7 +6497,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6537,7 +6507,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6552,22 +6527,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122719400</v>
+        <v>122721690</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>91397</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6576,38 +6551,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580956</v>
+        <v>581129</v>
       </c>
       <c r="R54" t="n">
-        <v>7057671</v>
+        <v>7057525</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6637,9 +6612,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6654,22 +6639,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122719963</v>
+        <v>122721757</v>
       </c>
       <c r="B55" t="n">
-        <v>78502</v>
+        <v>91243</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6682,34 +6667,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580966</v>
+        <v>581120</v>
       </c>
       <c r="R55" t="n">
-        <v>7057594</v>
+        <v>7057493</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6741,7 +6726,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6751,7 +6736,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6766,22 +6751,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122718678</v>
+        <v>122720577</v>
       </c>
       <c r="B56" t="n">
-        <v>78502</v>
+        <v>78411</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6794,21 +6779,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6818,10 +6803,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581005</v>
+        <v>581103</v>
       </c>
       <c r="R56" t="n">
-        <v>7057691</v>
+        <v>7057525</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6853,7 +6838,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6863,7 +6848,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6878,22 +6863,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122719953</v>
+        <v>122720864</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6906,37 +6891,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>580942</v>
+        <v>581112</v>
       </c>
       <c r="R57" t="n">
-        <v>7057618</v>
+        <v>7057450</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6963,9 +6948,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6980,19 +6975,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122721655</v>
+        <v>122722549</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -7032,13 +7027,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581182</v>
+        <v>581043</v>
       </c>
       <c r="R58" t="n">
-        <v>7057497</v>
+        <v>7057689</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7067,7 +7062,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7077,7 +7072,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7092,22 +7087,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122719828</v>
+        <v>122721655</v>
       </c>
       <c r="B59" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7116,46 +7111,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580901</v>
+        <v>581182</v>
       </c>
       <c r="R59" t="n">
-        <v>7057649</v>
+        <v>7057497</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7184,7 +7174,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7194,7 +7184,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7221,10 +7211,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122719130</v>
+        <v>122721746</v>
       </c>
       <c r="B60" t="n">
-        <v>79847</v>
+        <v>91397</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7233,25 +7223,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7261,10 +7251,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580985</v>
+        <v>581131</v>
       </c>
       <c r="R60" t="n">
-        <v>7057694</v>
+        <v>7057499</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7296,7 +7286,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7306,7 +7296,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7321,22 +7311,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122720864</v>
+        <v>122719963</v>
       </c>
       <c r="B61" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7349,37 +7339,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581112</v>
+        <v>580966</v>
       </c>
       <c r="R61" t="n">
-        <v>7057450</v>
+        <v>7057594</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7408,7 +7398,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7418,7 +7408,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7445,10 +7435,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122718748</v>
+        <v>122721907</v>
       </c>
       <c r="B62" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7457,31 +7447,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7490,10 +7480,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581004</v>
+        <v>581134</v>
       </c>
       <c r="R62" t="n">
-        <v>7057692</v>
+        <v>7057504</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7525,7 +7515,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7535,7 +7525,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7562,10 +7552,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122718499</v>
+        <v>122720546</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7578,34 +7568,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580999</v>
+        <v>581075</v>
       </c>
       <c r="R63" t="n">
-        <v>7057695</v>
+        <v>7057498</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7637,7 +7632,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7647,7 +7642,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122720528</v>
+        <v>122720544</v>
       </c>
       <c r="B12" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581073</v>
+        <v>581116</v>
       </c>
       <c r="R12" t="n">
-        <v>7057503</v>
+        <v>7057570</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,22 +1920,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122720544</v>
+        <v>122719828</v>
       </c>
       <c r="B13" t="n">
-        <v>78502</v>
+        <v>56688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,38 +1944,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581116</v>
+        <v>580901</v>
       </c>
       <c r="R13" t="n">
-        <v>7057570</v>
+        <v>7057649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122719828</v>
+        <v>122718574</v>
       </c>
       <c r="B14" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,43 +2061,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580901</v>
+        <v>580996</v>
       </c>
       <c r="R14" t="n">
-        <v>7057649</v>
+        <v>7057711</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,22 +2149,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122718574</v>
+        <v>122720528</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,21 +2177,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580996</v>
+        <v>581073</v>
       </c>
       <c r="R15" t="n">
-        <v>7057711</v>
+        <v>7057503</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,12 +2261,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122721705</v>
+        <v>122720257</v>
       </c>
       <c r="B18" t="n">
         <v>78502</v>
@@ -2533,14 +2533,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581182</v>
+        <v>580942</v>
       </c>
       <c r="R18" t="n">
-        <v>7057497</v>
+        <v>7057618</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,19 +2570,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,22 +2587,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122718715</v>
+        <v>122720351</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2625,21 +2615,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2649,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581011</v>
+        <v>581082</v>
       </c>
       <c r="R19" t="n">
-        <v>7057695</v>
+        <v>7057561</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2694,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2709,22 +2699,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122721034</v>
+        <v>122720096</v>
       </c>
       <c r="B20" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,34 +2727,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581112</v>
+        <v>580942</v>
       </c>
       <c r="R20" t="n">
-        <v>7057450</v>
+        <v>7057618</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2794,21 +2784,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2817,23 +2797,38 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122720257</v>
+        <v>122721705</v>
       </c>
       <c r="B21" t="n">
         <v>78502</v>
@@ -2869,14 +2864,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580942</v>
+        <v>581182</v>
       </c>
       <c r="R21" t="n">
-        <v>7057618</v>
+        <v>7057497</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2906,9 +2901,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2923,22 +2928,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122720351</v>
+        <v>122718715</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,21 +2956,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2975,10 +2980,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581082</v>
+        <v>581011</v>
       </c>
       <c r="R22" t="n">
-        <v>7057561</v>
+        <v>7057695</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,22 +3040,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122720096</v>
+        <v>122721034</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,34 +3068,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580942</v>
+        <v>581112</v>
       </c>
       <c r="R23" t="n">
-        <v>7057618</v>
+        <v>7057450</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,11 +3125,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3133,31 +3148,16 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122718499</v>
+        <v>122719214</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3614,41 +3614,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580999</v>
+        <v>580978</v>
       </c>
       <c r="R28" t="n">
-        <v>7057695</v>
+        <v>7057665</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3677,7 +3682,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3687,7 +3692,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3702,22 +3707,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122722568</v>
+        <v>122719130</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3730,21 +3735,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3754,10 +3759,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581036</v>
+        <v>580985</v>
       </c>
       <c r="R29" t="n">
-        <v>7057698</v>
+        <v>7057694</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3789,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3799,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,22 +3819,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122719214</v>
+        <v>122719600</v>
       </c>
       <c r="B30" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3838,46 +3843,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580978</v>
+        <v>580956</v>
       </c>
       <c r="R30" t="n">
-        <v>7057665</v>
+        <v>7057671</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3904,21 +3904,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3927,26 +3917,41 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122719130</v>
+        <v>122718499</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3959,21 +3964,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3983,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580985</v>
+        <v>580999</v>
       </c>
       <c r="R31" t="n">
-        <v>7057694</v>
+        <v>7057695</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4018,7 +4023,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4028,7 +4033,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4055,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122719600</v>
+        <v>122722568</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4071,34 +4076,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580956</v>
+        <v>581036</v>
       </c>
       <c r="R32" t="n">
-        <v>7057671</v>
+        <v>7057698</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4128,11 +4133,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4141,41 +4156,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122722473</v>
+        <v>122721195</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4188,21 +4188,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581086</v>
+        <v>581116</v>
       </c>
       <c r="R33" t="n">
-        <v>7057686</v>
+        <v>7057434</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4245,19 +4245,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4272,22 +4262,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122721195</v>
+        <v>122720385</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4300,21 +4290,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4324,10 +4314,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581116</v>
+        <v>581098</v>
       </c>
       <c r="R34" t="n">
-        <v>7057434</v>
+        <v>7057575</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4357,9 +4347,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4374,19 +4374,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122720385</v>
+        <v>122719411</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4422,17 +4422,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581098</v>
+        <v>580961</v>
       </c>
       <c r="R35" t="n">
-        <v>7057575</v>
+        <v>7057655</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,7 +4498,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122719411</v>
+        <v>122722537</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4534,17 +4534,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580961</v>
+        <v>581065</v>
       </c>
       <c r="R36" t="n">
-        <v>7057655</v>
+        <v>7057691</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4610,7 +4610,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122722537</v>
+        <v>122722473</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581065</v>
+        <v>581086</v>
       </c>
       <c r="R37" t="n">
-        <v>7057691</v>
+        <v>7057686</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4710,12 +4710,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5063,10 +5063,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122720457</v>
+        <v>122719696</v>
       </c>
       <c r="B41" t="n">
-        <v>57494</v>
+        <v>78411</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5079,39 +5079,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581081</v>
+        <v>580901</v>
       </c>
       <c r="R41" t="n">
-        <v>7057535</v>
+        <v>7057649</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5143,7 +5138,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5148,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5168,22 +5163,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122719696</v>
+        <v>122720457</v>
       </c>
       <c r="B42" t="n">
-        <v>78411</v>
+        <v>57494</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5196,34 +5191,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580901</v>
+        <v>581081</v>
       </c>
       <c r="R42" t="n">
-        <v>7057649</v>
+        <v>7057535</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5280,12 +5280,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122721504</v>
+        <v>122719444</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5883,34 +5883,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581165</v>
+        <v>580956</v>
       </c>
       <c r="R48" t="n">
-        <v>7057471</v>
+        <v>7057671</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5940,19 +5940,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5967,19 +5957,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122719444</v>
+        <v>122718678</v>
       </c>
       <c r="B49" t="n">
         <v>78502</v>
@@ -6015,14 +6005,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580956</v>
+        <v>581005</v>
       </c>
       <c r="R49" t="n">
-        <v>7057671</v>
+        <v>7057691</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6052,9 +6042,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6069,22 +6069,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122718678</v>
+        <v>122721504</v>
       </c>
       <c r="B50" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6097,21 +6097,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581005</v>
+        <v>581165</v>
       </c>
       <c r="R50" t="n">
-        <v>7057691</v>
+        <v>7057471</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6651,10 +6651,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122721757</v>
+        <v>122722549</v>
       </c>
       <c r="B55" t="n">
-        <v>91243</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6667,21 +6667,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6691,10 +6691,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581120</v>
+        <v>581043</v>
       </c>
       <c r="R55" t="n">
-        <v>7057493</v>
+        <v>7057689</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6751,22 +6751,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122720577</v>
+        <v>122721655</v>
       </c>
       <c r="B56" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6779,21 +6779,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6803,13 +6803,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581103</v>
+        <v>581182</v>
       </c>
       <c r="R56" t="n">
-        <v>7057525</v>
+        <v>7057497</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6875,10 +6875,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122720864</v>
+        <v>122721757</v>
       </c>
       <c r="B57" t="n">
-        <v>79847</v>
+        <v>91243</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6891,21 +6891,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6915,13 +6915,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581112</v>
+        <v>581120</v>
       </c>
       <c r="R57" t="n">
-        <v>7057450</v>
+        <v>7057493</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6975,22 +6975,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122722549</v>
+        <v>122720577</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7003,21 +7003,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7027,10 +7027,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581043</v>
+        <v>581103</v>
       </c>
       <c r="R58" t="n">
-        <v>7057689</v>
+        <v>7057525</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7087,22 +7087,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122721655</v>
+        <v>122720864</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7115,21 +7115,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7139,10 +7139,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581182</v>
+        <v>581112</v>
       </c>
       <c r="R59" t="n">
-        <v>7057497</v>
+        <v>7057450</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122721113</v>
+        <v>122721338</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581208</v>
+        <v>581145</v>
       </c>
       <c r="R2" t="n">
-        <v>7057415</v>
+        <v>7057410</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721338</v>
+        <v>122721113</v>
       </c>
       <c r="B4" t="n">
-        <v>78502</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581145</v>
+        <v>581208</v>
       </c>
       <c r="R4" t="n">
-        <v>7057410</v>
+        <v>7057415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122721003</v>
+        <v>122721690</v>
       </c>
       <c r="B5" t="n">
-        <v>78502</v>
+        <v>91397</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581112</v>
+        <v>581129</v>
       </c>
       <c r="R5" t="n">
-        <v>7057450</v>
+        <v>7057525</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122719585</v>
+        <v>122719214</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,41 +1140,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580901</v>
+        <v>580978</v>
       </c>
       <c r="R6" t="n">
-        <v>7057649</v>
+        <v>7057665</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122719175</v>
+        <v>122722059</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,13 +1285,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580984</v>
+        <v>581149</v>
       </c>
       <c r="R7" t="n">
-        <v>7057676</v>
+        <v>7057571</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1330,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,22 +1350,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122720063</v>
+        <v>122720577</v>
       </c>
       <c r="B8" t="n">
-        <v>78502</v>
+        <v>78411</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580986</v>
+        <v>581103</v>
       </c>
       <c r="R8" t="n">
-        <v>7057585</v>
+        <v>7057525</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1462,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122718748</v>
+        <v>122719250</v>
       </c>
       <c r="B9" t="n">
-        <v>56688</v>
+        <v>90952</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,43 +1486,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581004</v>
+        <v>580977</v>
       </c>
       <c r="R9" t="n">
-        <v>7057692</v>
+        <v>7057668</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122720911</v>
+        <v>122720864</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,21 +1602,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,13 +1626,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581101</v>
+        <v>581112</v>
       </c>
       <c r="R10" t="n">
-        <v>7057443</v>
+        <v>7057450</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1656,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,12 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,22 +1686,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122722336</v>
+        <v>122720544</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,39 +1714,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581102</v>
+        <v>581116</v>
       </c>
       <c r="R11" t="n">
-        <v>7057625</v>
+        <v>7057570</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,12 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,22 +1798,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122720544</v>
+        <v>122718499</v>
       </c>
       <c r="B12" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,21 +1826,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581116</v>
+        <v>580999</v>
       </c>
       <c r="R12" t="n">
-        <v>7057570</v>
+        <v>7057695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,22 +1910,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122719828</v>
+        <v>122722568</v>
       </c>
       <c r="B13" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,43 +1934,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580901</v>
+        <v>581036</v>
       </c>
       <c r="R13" t="n">
-        <v>7057649</v>
+        <v>7057698</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,22 +2022,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122718574</v>
+        <v>122720257</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,34 +2050,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580996</v>
+        <v>580942</v>
       </c>
       <c r="R14" t="n">
-        <v>7057711</v>
+        <v>7057618</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,19 +2107,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,22 +2124,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122720528</v>
+        <v>122719444</v>
       </c>
       <c r="B15" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,34 +2152,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581073</v>
+        <v>580956</v>
       </c>
       <c r="R15" t="n">
-        <v>7057503</v>
+        <v>7057671</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,19 +2209,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,22 +2226,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122719250</v>
+        <v>122720546</v>
       </c>
       <c r="B16" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,34 +2254,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580977</v>
+        <v>581075</v>
       </c>
       <c r="R16" t="n">
-        <v>7057668</v>
+        <v>7057498</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2328,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122719442</v>
+        <v>122719696</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>78411</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,21 +2376,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2425,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580912</v>
+        <v>580901</v>
       </c>
       <c r="R17" t="n">
-        <v>7057652</v>
+        <v>7057649</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2460,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122720257</v>
+        <v>122719175</v>
       </c>
       <c r="B18" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,37 +2488,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580942</v>
+        <v>580984</v>
       </c>
       <c r="R18" t="n">
-        <v>7057618</v>
+        <v>7057676</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2570,9 +2545,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2587,22 +2572,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122720351</v>
+        <v>122721034</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,21 +2600,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2639,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581082</v>
+        <v>581112</v>
       </c>
       <c r="R19" t="n">
-        <v>7057561</v>
+        <v>7057450</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2674,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122720096</v>
+        <v>122720911</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,34 +2712,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580942</v>
+        <v>581101</v>
       </c>
       <c r="R20" t="n">
-        <v>7057618</v>
+        <v>7057443</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,11 +2769,26 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2797,41 +2797,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122721705</v>
+        <v>122718574</v>
       </c>
       <c r="B21" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2844,21 +2829,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2868,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581182</v>
+        <v>580996</v>
       </c>
       <c r="R21" t="n">
-        <v>7057497</v>
+        <v>7057711</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,19 +2913,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122718715</v>
+        <v>122719130</v>
       </c>
       <c r="B22" t="n">
         <v>79847</v>
@@ -2980,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581011</v>
+        <v>580985</v>
       </c>
       <c r="R22" t="n">
-        <v>7057695</v>
+        <v>7057694</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122721034</v>
+        <v>122719600</v>
       </c>
       <c r="B23" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3068,34 +3053,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581112</v>
+        <v>580956</v>
       </c>
       <c r="R23" t="n">
-        <v>7057450</v>
+        <v>7057671</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3125,21 +3110,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3148,26 +3123,41 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122721161</v>
+        <v>122721757</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>91243</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3180,34 +3170,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581208</v>
+        <v>581120</v>
       </c>
       <c r="R24" t="n">
-        <v>7057450</v>
+        <v>7057493</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3239,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,7 +3266,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122719953</v>
+        <v>122719411</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3316,13 +3306,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580942</v>
+        <v>580961</v>
       </c>
       <c r="R25" t="n">
-        <v>7057618</v>
+        <v>7057655</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3349,9 +3339,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3366,22 +3366,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122720827</v>
+        <v>122719963</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3394,34 +3394,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581102</v>
+        <v>580966</v>
       </c>
       <c r="R26" t="n">
-        <v>7057553</v>
+        <v>7057594</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3602,10 +3602,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122719214</v>
+        <v>122720478</v>
       </c>
       <c r="B28" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3614,46 +3614,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580978</v>
+        <v>581116</v>
       </c>
       <c r="R28" t="n">
-        <v>7057665</v>
+        <v>7057570</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3682,7 +3677,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3692,7 +3687,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3719,10 +3714,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122719130</v>
+        <v>122722537</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3735,21 +3730,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3759,10 +3754,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580985</v>
+        <v>581065</v>
       </c>
       <c r="R29" t="n">
-        <v>7057694</v>
+        <v>7057691</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3794,7 +3789,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,7 +3799,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3819,19 +3814,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122719600</v>
+        <v>122721161</v>
       </c>
       <c r="B30" t="n">
         <v>79847</v>
@@ -3871,10 +3866,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580956</v>
+        <v>581208</v>
       </c>
       <c r="R30" t="n">
-        <v>7057671</v>
+        <v>7057450</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3904,11 +3899,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3917,41 +3922,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122718499</v>
+        <v>122722071</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3964,34 +3954,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580999</v>
+        <v>581148</v>
       </c>
       <c r="R31" t="n">
-        <v>7057695</v>
+        <v>7057575</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4023,7 +4018,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +4028,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122722568</v>
+        <v>122720063</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581036</v>
+        <v>580986</v>
       </c>
       <c r="R32" t="n">
-        <v>7057698</v>
+        <v>7057585</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4160,22 +4160,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122721195</v>
+        <v>122721655</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4188,21 +4188,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4212,13 +4212,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581116</v>
+        <v>581182</v>
       </c>
       <c r="R33" t="n">
-        <v>7057434</v>
+        <v>7057497</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4245,9 +4245,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4262,22 +4272,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122720385</v>
+        <v>122719558</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4290,34 +4300,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581098</v>
+        <v>580907</v>
       </c>
       <c r="R34" t="n">
-        <v>7057575</v>
+        <v>7057652</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,7 +4359,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4359,7 +4369,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4386,7 +4396,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122719411</v>
+        <v>122722549</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4422,17 +4432,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580961</v>
+        <v>581043</v>
       </c>
       <c r="R35" t="n">
-        <v>7057655</v>
+        <v>7057689</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4461,7 +4471,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,7 +4481,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4486,19 +4496,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122722537</v>
+        <v>122719953</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4534,14 +4544,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581065</v>
+        <v>580942</v>
       </c>
       <c r="R36" t="n">
-        <v>7057691</v>
+        <v>7057618</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4571,19 +4581,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4598,12 +4598,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4722,7 +4722,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122720361</v>
+        <v>122721705</v>
       </c>
       <c r="B38" t="n">
         <v>78502</v>
@@ -4762,13 +4762,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581082</v>
+        <v>581182</v>
       </c>
       <c r="R38" t="n">
-        <v>7057561</v>
+        <v>7057497</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4834,10 +4834,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122719531</v>
+        <v>122722701</v>
       </c>
       <c r="B39" t="n">
-        <v>79848</v>
+        <v>57494</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4850,37 +4850,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580913</v>
+        <v>581065</v>
       </c>
       <c r="R39" t="n">
-        <v>7057655</v>
+        <v>7057691</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4909,7 +4914,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4919,7 +4924,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4934,22 +4939,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122722059</v>
+        <v>122718748</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4958,38 +4963,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581149</v>
+        <v>581004</v>
       </c>
       <c r="R40" t="n">
-        <v>7057571</v>
+        <v>7057692</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5021,7 +5031,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5031,12 +5041,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5051,22 +5056,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122719696</v>
+        <v>122720361</v>
       </c>
       <c r="B41" t="n">
-        <v>78411</v>
+        <v>78502</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5079,37 +5084,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580901</v>
+        <v>581082</v>
       </c>
       <c r="R41" t="n">
-        <v>7057649</v>
+        <v>7057561</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5148,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5175,10 +5180,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122720457</v>
+        <v>122719531</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>79848</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5191,39 +5196,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581081</v>
+        <v>580913</v>
       </c>
       <c r="R42" t="n">
-        <v>7057535</v>
+        <v>7057655</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5280,22 +5280,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122720478</v>
+        <v>122722057</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5308,34 +5308,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581116</v>
+        <v>581149</v>
       </c>
       <c r="R43" t="n">
-        <v>7057570</v>
+        <v>7057577</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5367,7 +5372,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5377,7 +5382,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5392,22 +5402,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122722222</v>
+        <v>122721746</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>91397</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5416,43 +5426,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581129</v>
+        <v>581131</v>
       </c>
       <c r="R44" t="n">
-        <v>7057634</v>
+        <v>7057499</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5484,7 +5489,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5494,12 +5499,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5514,22 +5514,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122719400</v>
+        <v>122719461</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5542,21 +5542,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580956</v>
+        <v>580912</v>
       </c>
       <c r="R45" t="n">
-        <v>7057671</v>
+        <v>7057652</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5599,9 +5599,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5616,22 +5626,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122722701</v>
+        <v>122719585</v>
       </c>
       <c r="B46" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5644,42 +5654,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581065</v>
+        <v>580901</v>
       </c>
       <c r="R46" t="n">
-        <v>7057691</v>
+        <v>7057649</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5708,7 +5713,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5718,7 +5723,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5745,10 +5750,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122722071</v>
+        <v>122720096</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5761,39 +5766,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581148</v>
+        <v>580942</v>
       </c>
       <c r="R47" t="n">
-        <v>7057575</v>
+        <v>7057618</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5823,26 +5823,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5851,26 +5836,41 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122719444</v>
+        <v>122720366</v>
       </c>
       <c r="B48" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5883,34 +5883,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580956</v>
+        <v>581078</v>
       </c>
       <c r="R48" t="n">
-        <v>7057671</v>
+        <v>7057568</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5940,9 +5940,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5957,22 +5967,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122718678</v>
+        <v>122720827</v>
       </c>
       <c r="B49" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5985,21 +5995,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6009,10 +6019,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581005</v>
+        <v>581102</v>
       </c>
       <c r="R49" t="n">
-        <v>7057691</v>
+        <v>7057553</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6044,7 +6054,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6054,7 +6064,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6069,22 +6079,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122721504</v>
+        <v>122721003</v>
       </c>
       <c r="B50" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6097,21 +6107,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6121,13 +6131,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581165</v>
+        <v>581112</v>
       </c>
       <c r="R50" t="n">
-        <v>7057471</v>
+        <v>7057450</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6156,7 +6166,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6166,7 +6176,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6181,22 +6191,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122719558</v>
+        <v>122721907</v>
       </c>
       <c r="B51" t="n">
-        <v>79848</v>
+        <v>57494</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6209,34 +6219,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580907</v>
+        <v>581134</v>
       </c>
       <c r="R51" t="n">
-        <v>7057652</v>
+        <v>7057504</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6268,7 +6283,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6278,7 +6293,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6293,22 +6308,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122720366</v>
+        <v>122720385</v>
       </c>
       <c r="B52" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6321,21 +6336,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6345,10 +6360,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581078</v>
+        <v>581098</v>
       </c>
       <c r="R52" t="n">
-        <v>7057568</v>
+        <v>7057575</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6417,10 +6432,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122722057</v>
+        <v>122719828</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6429,43 +6444,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581149</v>
+        <v>580901</v>
       </c>
       <c r="R53" t="n">
-        <v>7057577</v>
+        <v>7057649</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6497,7 +6512,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6507,12 +6522,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,22 +6537,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122721690</v>
+        <v>122722222</v>
       </c>
       <c r="B54" t="n">
-        <v>91397</v>
+        <v>57478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6551,28 +6561,33 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
@@ -6582,7 +6597,7 @@
         <v>581129</v>
       </c>
       <c r="R54" t="n">
-        <v>7057525</v>
+        <v>7057634</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6614,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6624,7 +6639,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6651,10 +6671,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122722549</v>
+        <v>122721504</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6667,21 +6687,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6691,10 +6711,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581043</v>
+        <v>581165</v>
       </c>
       <c r="R55" t="n">
-        <v>7057689</v>
+        <v>7057471</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6726,7 +6746,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6736,7 +6756,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6763,10 +6783,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122721655</v>
+        <v>122721195</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6779,21 +6799,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6803,13 +6823,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581182</v>
+        <v>581116</v>
       </c>
       <c r="R56" t="n">
-        <v>7057497</v>
+        <v>7057434</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6836,19 +6856,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6863,22 +6873,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122721757</v>
+        <v>122718715</v>
       </c>
       <c r="B57" t="n">
-        <v>91243</v>
+        <v>79847</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6891,21 +6901,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6915,10 +6925,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581120</v>
+        <v>581011</v>
       </c>
       <c r="R57" t="n">
-        <v>7057493</v>
+        <v>7057695</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6950,7 +6960,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6960,7 +6970,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6975,22 +6985,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122720577</v>
+        <v>122722336</v>
       </c>
       <c r="B58" t="n">
-        <v>78411</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7003,34 +7013,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581103</v>
+        <v>581102</v>
       </c>
       <c r="R58" t="n">
-        <v>7057525</v>
+        <v>7057625</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7062,7 +7077,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7072,7 +7087,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7087,22 +7107,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122720864</v>
+        <v>122719400</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7115,37 +7135,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581112</v>
+        <v>580956</v>
       </c>
       <c r="R59" t="n">
-        <v>7057450</v>
+        <v>7057671</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7172,19 +7192,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7199,22 +7209,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122721746</v>
+        <v>122720457</v>
       </c>
       <c r="B60" t="n">
-        <v>91397</v>
+        <v>57494</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7223,38 +7233,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581131</v>
+        <v>581081</v>
       </c>
       <c r="R60" t="n">
-        <v>7057499</v>
+        <v>7057535</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7286,7 +7301,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7296,7 +7311,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7323,10 +7338,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122719963</v>
+        <v>122720528</v>
       </c>
       <c r="B61" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7339,34 +7354,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580966</v>
+        <v>581073</v>
       </c>
       <c r="R61" t="n">
-        <v>7057594</v>
+        <v>7057503</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7398,7 +7413,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7408,7 +7423,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7423,22 +7438,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122721907</v>
+        <v>122720351</v>
       </c>
       <c r="B62" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7451,39 +7466,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581134</v>
+        <v>581082</v>
       </c>
       <c r="R62" t="n">
-        <v>7057504</v>
+        <v>7057561</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7515,7 +7525,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7525,7 +7535,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7540,22 +7550,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122720546</v>
+        <v>122718678</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7568,39 +7578,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581075</v>
+        <v>581005</v>
       </c>
       <c r="R63" t="n">
-        <v>7057498</v>
+        <v>7057691</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7632,7 +7637,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7642,12 +7647,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122720544</v>
+        <v>122718499</v>
       </c>
       <c r="B11" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581116</v>
+        <v>580999</v>
       </c>
       <c r="R11" t="n">
-        <v>7057570</v>
+        <v>7057695</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,19 +1798,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122718499</v>
+        <v>122722568</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580999</v>
+        <v>581036</v>
       </c>
       <c r="R12" t="n">
-        <v>7057695</v>
+        <v>7057698</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,22 +1910,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122722568</v>
+        <v>122720544</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1938,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581036</v>
+        <v>581116</v>
       </c>
       <c r="R13" t="n">
-        <v>7057698</v>
+        <v>7057570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,12 +2022,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122719444</v>
+        <v>122720546</v>
       </c>
       <c r="B15" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,34 +2152,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580956</v>
+        <v>581075</v>
       </c>
       <c r="R15" t="n">
-        <v>7057671</v>
+        <v>7057498</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,9 +2214,24 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,22 +2246,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122720546</v>
+        <v>122719696</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>78411</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,39 +2274,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581075</v>
+        <v>580901</v>
       </c>
       <c r="R16" t="n">
-        <v>7057498</v>
+        <v>7057649</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2318,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,12 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,22 +2358,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122719696</v>
+        <v>122719175</v>
       </c>
       <c r="B17" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,37 +2386,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580901</v>
+        <v>580984</v>
       </c>
       <c r="R17" t="n">
-        <v>7057649</v>
+        <v>7057676</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2435,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122719175</v>
+        <v>122719444</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,37 +2498,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580984</v>
+        <v>580956</v>
       </c>
       <c r="R18" t="n">
-        <v>7057676</v>
+        <v>7057671</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2545,19 +2555,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,22 +2572,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122721034</v>
+        <v>122718574</v>
       </c>
       <c r="B19" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,21 +2600,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581112</v>
+        <v>580996</v>
       </c>
       <c r="R19" t="n">
-        <v>7057450</v>
+        <v>7057711</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,22 +2684,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122720911</v>
+        <v>122719130</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,21 +2712,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581101</v>
+        <v>580985</v>
       </c>
       <c r="R20" t="n">
-        <v>7057443</v>
+        <v>7057694</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,12 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,19 +2796,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122718574</v>
+        <v>122719600</v>
       </c>
       <c r="B21" t="n">
         <v>79847</v>
@@ -2849,14 +2844,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580996</v>
+        <v>580956</v>
       </c>
       <c r="R21" t="n">
-        <v>7057711</v>
+        <v>7057671</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2886,21 +2881,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2909,26 +2894,41 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122719130</v>
+        <v>122720911</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,21 +2941,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580985</v>
+        <v>581101</v>
       </c>
       <c r="R22" t="n">
-        <v>7057694</v>
+        <v>7057443</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3010,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,22 +3030,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122719600</v>
+        <v>122721034</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,34 +3058,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580956</v>
+        <v>581112</v>
       </c>
       <c r="R23" t="n">
-        <v>7057671</v>
+        <v>7057450</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3110,11 +3115,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3123,31 +3138,16 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122720063</v>
+        <v>122721655</v>
       </c>
       <c r="B32" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,13 +4100,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580986</v>
+        <v>581182</v>
       </c>
       <c r="R32" t="n">
-        <v>7057585</v>
+        <v>7057497</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4160,22 +4160,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122721655</v>
+        <v>122720063</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4188,21 +4188,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4212,13 +4212,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581182</v>
+        <v>580986</v>
       </c>
       <c r="R33" t="n">
-        <v>7057497</v>
+        <v>7057585</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4272,12 +4272,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -2584,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122718574</v>
+        <v>122721034</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,21 +2600,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580996</v>
+        <v>581112</v>
       </c>
       <c r="R19" t="n">
-        <v>7057711</v>
+        <v>7057450</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,22 +2684,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122719130</v>
+        <v>122720911</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,21 +2712,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580985</v>
+        <v>581101</v>
       </c>
       <c r="R20" t="n">
-        <v>7057694</v>
+        <v>7057443</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2781,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,19 +2801,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122719600</v>
+        <v>122718574</v>
       </c>
       <c r="B21" t="n">
         <v>79847</v>
@@ -2844,14 +2849,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580956</v>
+        <v>580996</v>
       </c>
       <c r="R21" t="n">
-        <v>7057671</v>
+        <v>7057711</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2881,11 +2886,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2894,41 +2909,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122720911</v>
+        <v>122719130</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,21 +2941,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581101</v>
+        <v>580985</v>
       </c>
       <c r="R22" t="n">
-        <v>7057443</v>
+        <v>7057694</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,12 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,22 +3025,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122721034</v>
+        <v>122719600</v>
       </c>
       <c r="B23" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3058,34 +3053,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581112</v>
+        <v>580956</v>
       </c>
       <c r="R23" t="n">
-        <v>7057450</v>
+        <v>7057671</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3115,21 +3110,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3138,16 +3123,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122722537</v>
+        <v>122722071</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3730,34 +3730,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581065</v>
+        <v>581148</v>
       </c>
       <c r="R29" t="n">
-        <v>7057691</v>
+        <v>7057575</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3789,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3799,7 +3804,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,22 +3824,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122721161</v>
+        <v>122722537</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3842,34 +3852,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581208</v>
+        <v>581065</v>
       </c>
       <c r="R30" t="n">
-        <v>7057450</v>
+        <v>7057691</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3901,7 +3911,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3911,7 +3921,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3926,22 +3936,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122722071</v>
+        <v>122721161</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3954,39 +3964,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581148</v>
+        <v>581208</v>
       </c>
       <c r="R31" t="n">
-        <v>7057575</v>
+        <v>7057450</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4018,7 +4023,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4028,12 +4033,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4048,12 +4048,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5068,10 +5068,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122720361</v>
+        <v>122721746</v>
       </c>
       <c r="B41" t="n">
-        <v>78502</v>
+        <v>91397</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5080,25 +5080,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5108,13 +5108,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581082</v>
+        <v>581131</v>
       </c>
       <c r="R41" t="n">
-        <v>7057561</v>
+        <v>7057499</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5168,22 +5168,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122719531</v>
+        <v>122720361</v>
       </c>
       <c r="B42" t="n">
-        <v>79848</v>
+        <v>78502</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5196,21 +5196,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5220,13 +5220,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580913</v>
+        <v>581082</v>
       </c>
       <c r="R42" t="n">
-        <v>7057655</v>
+        <v>7057561</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5280,22 +5280,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122722057</v>
+        <v>122719531</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5308,39 +5308,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581149</v>
+        <v>580913</v>
       </c>
       <c r="R43" t="n">
-        <v>7057577</v>
+        <v>7057655</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5372,7 +5367,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5382,12 +5377,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5414,10 +5404,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122721746</v>
+        <v>122722057</v>
       </c>
       <c r="B44" t="n">
-        <v>91397</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5426,38 +5416,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581131</v>
+        <v>581149</v>
       </c>
       <c r="R44" t="n">
-        <v>7057499</v>
+        <v>7057577</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5489,7 +5484,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5499,7 +5494,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5514,12 +5514,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6320,10 +6320,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122720385</v>
+        <v>122722222</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6336,34 +6336,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581098</v>
+        <v>581129</v>
       </c>
       <c r="R52" t="n">
-        <v>7057575</v>
+        <v>7057634</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6395,7 +6400,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6405,7 +6410,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6420,12 +6430,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6549,10 +6559,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122722222</v>
+        <v>122720385</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6565,39 +6575,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581129</v>
+        <v>581098</v>
       </c>
       <c r="R54" t="n">
-        <v>7057634</v>
+        <v>7057575</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6629,7 +6634,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,12 +6644,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6659,12 +6659,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122721690</v>
+        <v>122722336</v>
       </c>
       <c r="B5" t="n">
-        <v>91397</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,38 +1028,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581129</v>
+        <v>581102</v>
       </c>
       <c r="R5" t="n">
-        <v>7057525</v>
+        <v>7057625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122719214</v>
+        <v>122720528</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
+        <v>78503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,46 +1150,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580978</v>
+        <v>581073</v>
       </c>
       <c r="R6" t="n">
-        <v>7057665</v>
+        <v>7057503</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1238,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122722059</v>
+        <v>122720577</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78411</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581149</v>
+        <v>581103</v>
       </c>
       <c r="R7" t="n">
-        <v>7057571</v>
+        <v>7057525</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,12 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,22 +1350,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122720577</v>
+        <v>122720361</v>
       </c>
       <c r="B8" t="n">
-        <v>78411</v>
+        <v>78502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,13 +1402,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581103</v>
+        <v>581082</v>
       </c>
       <c r="R8" t="n">
-        <v>7057525</v>
+        <v>7057561</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122719250</v>
+        <v>122719558</v>
       </c>
       <c r="B9" t="n">
-        <v>90952</v>
+        <v>79848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,34 +1490,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580977</v>
+        <v>580907</v>
       </c>
       <c r="R9" t="n">
-        <v>7057668</v>
+        <v>7057652</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,22 +1574,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122720864</v>
+        <v>122722568</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,21 +1602,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581112</v>
+        <v>581036</v>
       </c>
       <c r="R10" t="n">
-        <v>7057450</v>
+        <v>7057698</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,22 +1686,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122718499</v>
+        <v>122719442</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,34 +1714,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580999</v>
+        <v>580912</v>
       </c>
       <c r="R11" t="n">
-        <v>7057695</v>
+        <v>7057652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,22 +1798,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122722568</v>
+        <v>122720063</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,21 +1826,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581036</v>
+        <v>580986</v>
       </c>
       <c r="R12" t="n">
-        <v>7057698</v>
+        <v>7057585</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,22 +1910,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122720544</v>
+        <v>122720351</v>
       </c>
       <c r="B13" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1938,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581116</v>
+        <v>581082</v>
       </c>
       <c r="R13" t="n">
-        <v>7057570</v>
+        <v>7057561</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122720257</v>
+        <v>122721034</v>
       </c>
       <c r="B14" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,34 +2050,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580942</v>
+        <v>581112</v>
       </c>
       <c r="R14" t="n">
-        <v>7057618</v>
+        <v>7057450</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,9 +2107,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,19 +2134,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122720546</v>
+        <v>122722059</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2170,21 +2180,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581075</v>
+        <v>581149</v>
       </c>
       <c r="R15" t="n">
-        <v>7057498</v>
+        <v>7057571</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2246,22 +2251,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122719696</v>
+        <v>122719585</v>
       </c>
       <c r="B16" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,21 +2279,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2333,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122719175</v>
+        <v>122719696</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,37 +2391,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580984</v>
+        <v>580901</v>
       </c>
       <c r="R17" t="n">
-        <v>7057676</v>
+        <v>7057649</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2445,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122719444</v>
+        <v>122721746</v>
       </c>
       <c r="B18" t="n">
-        <v>78502</v>
+        <v>91397</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2494,38 +2499,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580956</v>
+        <v>581131</v>
       </c>
       <c r="R18" t="n">
-        <v>7057671</v>
+        <v>7057499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,9 +2560,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,22 +2587,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122721034</v>
+        <v>122721705</v>
       </c>
       <c r="B19" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,21 +2615,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581112</v>
+        <v>581182</v>
       </c>
       <c r="R19" t="n">
-        <v>7057450</v>
+        <v>7057497</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122720911</v>
+        <v>122721195</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,21 +2727,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581101</v>
+        <v>581116</v>
       </c>
       <c r="R20" t="n">
-        <v>7057443</v>
+        <v>7057434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2769,24 +2784,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,22 +2801,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122718574</v>
+        <v>122720546</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,34 +2829,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580996</v>
+        <v>581075</v>
       </c>
       <c r="R21" t="n">
-        <v>7057711</v>
+        <v>7057498</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2903,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122719130</v>
+        <v>122721003</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,21 +2951,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,13 +2975,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580985</v>
+        <v>581112</v>
       </c>
       <c r="R22" t="n">
-        <v>7057694</v>
+        <v>7057450</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3000,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,22 +3035,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122719600</v>
+        <v>122722549</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,34 +3063,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580956</v>
+        <v>581043</v>
       </c>
       <c r="R23" t="n">
-        <v>7057671</v>
+        <v>7057689</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3110,11 +3120,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3123,41 +3143,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122721757</v>
+        <v>122720278</v>
       </c>
       <c r="B24" t="n">
-        <v>91243</v>
+        <v>78502</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3170,34 +3175,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581120</v>
+        <v>580942</v>
       </c>
       <c r="R24" t="n">
-        <v>7057493</v>
+        <v>7057618</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3227,19 +3232,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3254,19 +3249,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122719411</v>
+        <v>122720458</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3302,17 +3297,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580961</v>
+        <v>581098</v>
       </c>
       <c r="R25" t="n">
-        <v>7057655</v>
+        <v>7057575</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3341,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3378,7 +3373,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122719963</v>
+        <v>122720544</v>
       </c>
       <c r="B26" t="n">
         <v>78502</v>
@@ -3414,14 +3409,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580966</v>
+        <v>581116</v>
       </c>
       <c r="R26" t="n">
-        <v>7057594</v>
+        <v>7057570</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3463,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3490,7 +3485,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122719358</v>
+        <v>122719963</v>
       </c>
       <c r="B27" t="n">
         <v>78502</v>
@@ -3530,10 +3525,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580961</v>
+        <v>580966</v>
       </c>
       <c r="R27" t="n">
-        <v>7057655</v>
+        <v>7057594</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3565,7 +3560,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3575,7 +3570,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,7 +3597,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122720478</v>
+        <v>122719411</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3638,17 +3633,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581116</v>
+        <v>580961</v>
       </c>
       <c r="R28" t="n">
-        <v>7057570</v>
+        <v>7057655</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3677,7 +3672,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3687,7 +3682,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,10 +3709,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122722071</v>
+        <v>122718499</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3730,39 +3725,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581148</v>
+        <v>580999</v>
       </c>
       <c r="R29" t="n">
-        <v>7057575</v>
+        <v>7057695</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3794,7 +3784,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,12 +3794,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3948,10 +3933,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122721161</v>
+        <v>122719444</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3964,21 +3949,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3988,10 +3973,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581208</v>
+        <v>580956</v>
       </c>
       <c r="R31" t="n">
-        <v>7057450</v>
+        <v>7057671</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4021,19 +4006,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4048,22 +4023,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122721655</v>
+        <v>122718715</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4076,21 +4051,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,13 +4075,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581182</v>
+        <v>581011</v>
       </c>
       <c r="R32" t="n">
-        <v>7057497</v>
+        <v>7057695</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4135,7 +4110,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4145,7 +4120,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4160,22 +4135,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122720063</v>
+        <v>122722071</v>
       </c>
       <c r="B33" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4188,34 +4163,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580986</v>
+        <v>581148</v>
       </c>
       <c r="R33" t="n">
-        <v>7057585</v>
+        <v>7057575</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,7 +4227,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4237,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,7 +4269,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122719558</v>
+        <v>122719531</v>
       </c>
       <c r="B34" t="n">
         <v>79848</v>
@@ -4320,14 +4305,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580907</v>
+        <v>580913</v>
       </c>
       <c r="R34" t="n">
-        <v>7057652</v>
+        <v>7057655</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4359,7 +4344,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4369,7 +4354,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4384,19 +4369,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122722549</v>
+        <v>122719175</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4436,13 +4421,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581043</v>
+        <v>580984</v>
       </c>
       <c r="R35" t="n">
-        <v>7057689</v>
+        <v>7057676</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4471,7 +4456,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4481,7 +4466,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4496,22 +4481,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122719953</v>
+        <v>122719250</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4524,34 +4509,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580942</v>
+        <v>580977</v>
       </c>
       <c r="R36" t="n">
-        <v>7057618</v>
+        <v>7057668</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4581,9 +4566,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4598,22 +4593,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122722473</v>
+        <v>122720096</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4626,34 +4621,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581086</v>
+        <v>580942</v>
       </c>
       <c r="R37" t="n">
-        <v>7057686</v>
+        <v>7057618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4683,21 +4678,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4706,26 +4691,41 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122721705</v>
+        <v>122719600</v>
       </c>
       <c r="B38" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4738,34 +4738,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581182</v>
+        <v>580956</v>
       </c>
       <c r="R38" t="n">
-        <v>7057497</v>
+        <v>7057671</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4795,21 +4795,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4818,26 +4808,41 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122722701</v>
+        <v>122721504</v>
       </c>
       <c r="B39" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4850,42 +4855,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581065</v>
+        <v>581165</v>
       </c>
       <c r="R39" t="n">
-        <v>7057691</v>
+        <v>7057471</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4939,22 +4939,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122718748</v>
+        <v>122720478</v>
       </c>
       <c r="B40" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4963,43 +4963,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581004</v>
+        <v>581116</v>
       </c>
       <c r="R40" t="n">
-        <v>7057692</v>
+        <v>7057570</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5031,7 +5026,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5041,7 +5036,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5056,22 +5051,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122721746</v>
+        <v>122719953</v>
       </c>
       <c r="B41" t="n">
-        <v>91397</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5080,38 +5075,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581131</v>
+        <v>580942</v>
       </c>
       <c r="R41" t="n">
-        <v>7057499</v>
+        <v>7057618</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5141,19 +5136,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5168,22 +5153,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122720361</v>
+        <v>122718748</v>
       </c>
       <c r="B42" t="n">
-        <v>78502</v>
+        <v>56688</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5192,41 +5177,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581082</v>
+        <v>581004</v>
       </c>
       <c r="R42" t="n">
-        <v>7057561</v>
+        <v>7057692</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5255,7 +5245,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5265,7 +5255,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5280,22 +5270,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122719531</v>
+        <v>122719828</v>
       </c>
       <c r="B43" t="n">
-        <v>79848</v>
+        <v>56688</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5304,38 +5294,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580913</v>
+        <v>580901</v>
       </c>
       <c r="R43" t="n">
-        <v>7057655</v>
+        <v>7057649</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5367,7 +5362,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5377,7 +5372,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5392,12 +5387,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5526,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122719461</v>
+        <v>122720911</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5542,34 +5537,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580912</v>
+        <v>581101</v>
       </c>
       <c r="R45" t="n">
-        <v>7057652</v>
+        <v>7057443</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5601,7 +5596,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5611,7 +5606,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5626,22 +5626,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122719585</v>
+        <v>122720457</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5654,34 +5654,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580901</v>
+        <v>581081</v>
       </c>
       <c r="R46" t="n">
-        <v>7057649</v>
+        <v>7057535</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5713,7 +5718,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5723,7 +5728,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5738,22 +5743,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122720096</v>
+        <v>122721690</v>
       </c>
       <c r="B47" t="n">
-        <v>79847</v>
+        <v>91397</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5762,38 +5767,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580942</v>
+        <v>581129</v>
       </c>
       <c r="R47" t="n">
-        <v>7057618</v>
+        <v>7057525</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5823,11 +5828,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5836,41 +5851,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122720366</v>
+        <v>122718678</v>
       </c>
       <c r="B48" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5883,21 +5883,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5907,10 +5907,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581078</v>
+        <v>581005</v>
       </c>
       <c r="R48" t="n">
-        <v>7057568</v>
+        <v>7057691</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5967,22 +5967,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122720827</v>
+        <v>122718574</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5995,21 +5995,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6019,10 +6019,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581102</v>
+        <v>580996</v>
       </c>
       <c r="R49" t="n">
-        <v>7057553</v>
+        <v>7057711</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6079,22 +6079,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122721003</v>
+        <v>122720366</v>
       </c>
       <c r="B50" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6107,21 +6107,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581112</v>
+        <v>581078</v>
       </c>
       <c r="R50" t="n">
-        <v>7057450</v>
+        <v>7057568</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6203,10 +6203,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122721907</v>
+        <v>122719214</v>
       </c>
       <c r="B51" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6215,31 +6215,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6248,13 +6248,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581134</v>
+        <v>580978</v>
       </c>
       <c r="R51" t="n">
-        <v>7057504</v>
+        <v>7057665</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6308,22 +6308,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122722222</v>
+        <v>122720864</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6336,42 +6336,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581129</v>
+        <v>581112</v>
       </c>
       <c r="R52" t="n">
-        <v>7057634</v>
+        <v>7057450</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6400,7 +6395,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6410,12 +6405,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6430,22 +6420,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122719828</v>
+        <v>122721161</v>
       </c>
       <c r="B53" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6454,43 +6444,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580901</v>
+        <v>581208</v>
       </c>
       <c r="R53" t="n">
-        <v>7057649</v>
+        <v>7057450</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6522,7 +6507,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6532,7 +6517,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6547,22 +6532,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122720385</v>
+        <v>122719130</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6575,21 +6560,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6599,10 +6584,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581098</v>
+        <v>580985</v>
       </c>
       <c r="R54" t="n">
-        <v>7057575</v>
+        <v>7057694</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6634,7 +6619,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6644,7 +6629,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6659,22 +6644,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122721504</v>
+        <v>122722473</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6687,21 +6672,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6711,10 +6696,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581165</v>
+        <v>581086</v>
       </c>
       <c r="R55" t="n">
-        <v>7057471</v>
+        <v>7057686</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6746,7 +6731,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6756,7 +6741,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6783,10 +6768,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122721195</v>
+        <v>122720827</v>
       </c>
       <c r="B56" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6799,21 +6784,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6823,10 +6808,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581116</v>
+        <v>581102</v>
       </c>
       <c r="R56" t="n">
-        <v>7057434</v>
+        <v>7057553</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6856,9 +6841,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6873,22 +6868,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122718715</v>
+        <v>122721907</v>
       </c>
       <c r="B57" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6901,34 +6896,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581011</v>
+        <v>581134</v>
       </c>
       <c r="R57" t="n">
-        <v>7057695</v>
+        <v>7057504</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6997,10 +6997,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122722336</v>
+        <v>122721757</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>91243</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7013,39 +7013,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581102</v>
+        <v>581120</v>
       </c>
       <c r="R58" t="n">
-        <v>7057625</v>
+        <v>7057493</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7077,7 +7072,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7087,12 +7082,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7107,22 +7097,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122719400</v>
+        <v>122722222</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7135,34 +7125,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580956</v>
+        <v>581129</v>
       </c>
       <c r="R59" t="n">
-        <v>7057671</v>
+        <v>7057634</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7192,9 +7187,24 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7209,22 +7219,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122720457</v>
+        <v>122719358</v>
       </c>
       <c r="B60" t="n">
-        <v>57494</v>
+        <v>78502</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7237,39 +7247,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581081</v>
+        <v>580961</v>
       </c>
       <c r="R60" t="n">
-        <v>7057535</v>
+        <v>7057655</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7301,7 +7306,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7311,7 +7316,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7326,22 +7331,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122720528</v>
+        <v>122722701</v>
       </c>
       <c r="B61" t="n">
-        <v>78503</v>
+        <v>57494</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7354,37 +7359,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581073</v>
+        <v>581065</v>
       </c>
       <c r="R61" t="n">
-        <v>7057503</v>
+        <v>7057691</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7413,7 +7423,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7423,7 +7433,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7438,19 +7448,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122720351</v>
+        <v>122721655</v>
       </c>
       <c r="B62" t="n">
         <v>78766</v>
@@ -7490,13 +7500,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581082</v>
+        <v>581182</v>
       </c>
       <c r="R62" t="n">
-        <v>7057561</v>
+        <v>7057497</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7525,7 +7535,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7535,7 +7545,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7562,10 +7572,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122718678</v>
+        <v>122719400</v>
       </c>
       <c r="B63" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7578,34 +7588,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581005</v>
+        <v>580956</v>
       </c>
       <c r="R63" t="n">
-        <v>7057691</v>
+        <v>7057671</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7635,19 +7645,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7662,12 +7662,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721501</v>
+        <v>122721113</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581145</v>
+        <v>581208</v>
       </c>
       <c r="R3" t="n">
-        <v>7057410</v>
+        <v>7057415</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721113</v>
+        <v>122721501</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,42 +920,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581208</v>
+        <v>581145</v>
       </c>
       <c r="R4" t="n">
-        <v>7057415</v>
+        <v>7057410</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122722336</v>
+        <v>122719455</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581102</v>
+        <v>580912</v>
       </c>
       <c r="R5" t="n">
-        <v>7057625</v>
+        <v>7057652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122720528</v>
+        <v>122720827</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581073</v>
+        <v>581102</v>
       </c>
       <c r="R6" t="n">
-        <v>7057503</v>
+        <v>7057553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122720577</v>
+        <v>122718499</v>
       </c>
       <c r="B7" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581103</v>
+        <v>580999</v>
       </c>
       <c r="R7" t="n">
-        <v>7057525</v>
+        <v>7057695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,22 +1340,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122720361</v>
+        <v>122721907</v>
       </c>
       <c r="B8" t="n">
-        <v>78502</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,37 +1368,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581082</v>
+        <v>581134</v>
       </c>
       <c r="R8" t="n">
-        <v>7057561</v>
+        <v>7057504</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,22 +1457,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122719558</v>
+        <v>122719600</v>
       </c>
       <c r="B9" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580907</v>
+        <v>580956</v>
       </c>
       <c r="R9" t="n">
-        <v>7057652</v>
+        <v>7057671</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,21 +1542,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1570,26 +1555,41 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122722568</v>
+        <v>122720361</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,21 +1602,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581036</v>
+        <v>581082</v>
       </c>
       <c r="R10" t="n">
-        <v>7057698</v>
+        <v>7057561</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,22 +1686,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122719442</v>
+        <v>122722057</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,34 +1714,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580912</v>
+        <v>581149</v>
       </c>
       <c r="R11" t="n">
-        <v>7057652</v>
+        <v>7057577</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1788,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,22 +1808,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122720063</v>
+        <v>122722549</v>
       </c>
       <c r="B12" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580986</v>
+        <v>581043</v>
       </c>
       <c r="R12" t="n">
-        <v>7057585</v>
+        <v>7057689</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,7 +1932,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122720351</v>
+        <v>122719400</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1958,14 +1968,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581082</v>
+        <v>580956</v>
       </c>
       <c r="R13" t="n">
-        <v>7057561</v>
+        <v>7057671</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,19 +2005,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,22 +2022,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122721034</v>
+        <v>122719558</v>
       </c>
       <c r="B14" t="n">
-        <v>78503</v>
+        <v>79848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,34 +2050,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581112</v>
+        <v>580907</v>
       </c>
       <c r="R14" t="n">
-        <v>7057450</v>
+        <v>7057652</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122722059</v>
+        <v>122720577</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>78411</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,21 +2162,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581149</v>
+        <v>581103</v>
       </c>
       <c r="R15" t="n">
-        <v>7057571</v>
+        <v>7057525</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,12 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,22 +2246,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122719585</v>
+        <v>122718715</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,34 +2274,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580901</v>
+        <v>581011</v>
       </c>
       <c r="R16" t="n">
-        <v>7057649</v>
+        <v>7057695</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,22 +2358,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122719696</v>
+        <v>122719953</v>
       </c>
       <c r="B17" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,21 +2386,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2415,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580901</v>
+        <v>580942</v>
       </c>
       <c r="R17" t="n">
-        <v>7057649</v>
+        <v>7057618</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,19 +2443,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2475,22 +2460,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122721746</v>
+        <v>122721655</v>
       </c>
       <c r="B18" t="n">
-        <v>91397</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,25 +2484,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2527,13 +2512,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581131</v>
+        <v>581182</v>
       </c>
       <c r="R18" t="n">
-        <v>7057499</v>
+        <v>7057497</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2562,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2587,22 +2572,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122721705</v>
+        <v>122722059</v>
       </c>
       <c r="B19" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,21 +2600,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2639,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581182</v>
+        <v>581149</v>
       </c>
       <c r="R19" t="n">
-        <v>7057497</v>
+        <v>7057571</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2674,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2669,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2699,22 +2689,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122721195</v>
+        <v>122722568</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,21 +2717,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2751,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581116</v>
+        <v>581036</v>
       </c>
       <c r="R20" t="n">
-        <v>7057434</v>
+        <v>7057698</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,9 +2774,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,22 +2801,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122720546</v>
+        <v>122718678</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,39 +2829,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581075</v>
+        <v>581005</v>
       </c>
       <c r="R21" t="n">
-        <v>7057498</v>
+        <v>7057691</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2893,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,12 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122721003</v>
+        <v>122718748</v>
       </c>
       <c r="B22" t="n">
-        <v>78502</v>
+        <v>56688</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,41 +2937,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581112</v>
+        <v>581004</v>
       </c>
       <c r="R22" t="n">
-        <v>7057450</v>
+        <v>7057692</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3010,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,22 +3030,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122722549</v>
+        <v>122720457</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,34 +3058,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581043</v>
+        <v>581081</v>
       </c>
       <c r="R23" t="n">
-        <v>7057689</v>
+        <v>7057535</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,22 +3147,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122720278</v>
+        <v>122721504</v>
       </c>
       <c r="B24" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,34 +3175,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580942</v>
+        <v>581165</v>
       </c>
       <c r="R24" t="n">
-        <v>7057618</v>
+        <v>7057471</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3232,9 +3232,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,19 +3259,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122720458</v>
+        <v>122719585</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3297,14 +3307,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581098</v>
+        <v>580901</v>
       </c>
       <c r="R25" t="n">
-        <v>7057575</v>
+        <v>7057649</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3336,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,10 +3383,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122720544</v>
+        <v>122722071</v>
       </c>
       <c r="B26" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,34 +3399,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581116</v>
+        <v>581148</v>
       </c>
       <c r="R26" t="n">
-        <v>7057570</v>
+        <v>7057575</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3448,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3473,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3473,22 +3493,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122719963</v>
+        <v>122719250</v>
       </c>
       <c r="B27" t="n">
-        <v>78502</v>
+        <v>90952</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,34 +3521,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580966</v>
+        <v>580977</v>
       </c>
       <c r="R27" t="n">
-        <v>7057594</v>
+        <v>7057668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3560,7 +3580,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3570,7 +3590,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3585,19 +3605,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122719411</v>
+        <v>122720351</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3633,17 +3653,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580961</v>
+        <v>581082</v>
       </c>
       <c r="R28" t="n">
-        <v>7057655</v>
+        <v>7057561</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3672,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3682,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,10 +3729,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122718499</v>
+        <v>122719130</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3725,21 +3745,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3749,10 +3769,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580999</v>
+        <v>580985</v>
       </c>
       <c r="R29" t="n">
-        <v>7057695</v>
+        <v>7057694</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3784,7 +3804,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3794,7 +3814,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3821,10 +3841,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122722537</v>
+        <v>122721161</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3837,34 +3857,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581065</v>
+        <v>581208</v>
       </c>
       <c r="R30" t="n">
-        <v>7057691</v>
+        <v>7057450</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3896,7 +3916,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3906,7 +3926,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3921,22 +3941,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122719444</v>
+        <v>122721746</v>
       </c>
       <c r="B31" t="n">
-        <v>78502</v>
+        <v>91397</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3945,38 +3965,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580956</v>
+        <v>581131</v>
       </c>
       <c r="R31" t="n">
-        <v>7057671</v>
+        <v>7057499</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4006,9 +4026,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4023,22 +4053,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122718715</v>
+        <v>122720478</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,21 +4081,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4075,10 +4105,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581011</v>
+        <v>581116</v>
       </c>
       <c r="R32" t="n">
-        <v>7057695</v>
+        <v>7057570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4110,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4120,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4135,22 +4165,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122722071</v>
+        <v>122722473</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4163,39 +4193,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581148</v>
+        <v>581086</v>
       </c>
       <c r="R33" t="n">
-        <v>7057575</v>
+        <v>7057686</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4227,7 +4252,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4237,12 +4262,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4269,10 +4289,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122719531</v>
+        <v>122721003</v>
       </c>
       <c r="B34" t="n">
-        <v>79848</v>
+        <v>78502</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4285,21 +4305,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4309,13 +4329,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580913</v>
+        <v>581112</v>
       </c>
       <c r="R34" t="n">
-        <v>7057655</v>
+        <v>7057450</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4344,7 +4364,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4354,7 +4374,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4369,22 +4389,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122719175</v>
+        <v>122719531</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4397,21 +4417,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4421,13 +4441,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580984</v>
+        <v>580913</v>
       </c>
       <c r="R35" t="n">
-        <v>7057676</v>
+        <v>7057655</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4456,7 +4476,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4466,7 +4486,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4481,22 +4501,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122719250</v>
+        <v>122720544</v>
       </c>
       <c r="B36" t="n">
-        <v>90952</v>
+        <v>78502</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4509,21 +4529,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4533,10 +4553,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580977</v>
+        <v>581116</v>
       </c>
       <c r="R36" t="n">
-        <v>7057668</v>
+        <v>7057570</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4568,7 +4588,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4578,7 +4598,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4593,22 +4613,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122720096</v>
+        <v>122721757</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>91243</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4621,34 +4641,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580942</v>
+        <v>581120</v>
       </c>
       <c r="R37" t="n">
-        <v>7057618</v>
+        <v>7057493</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4678,11 +4698,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4691,41 +4721,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122719600</v>
+        <v>122720458</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4738,34 +4753,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580956</v>
+        <v>581098</v>
       </c>
       <c r="R38" t="n">
-        <v>7057671</v>
+        <v>7057575</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4795,11 +4810,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4808,41 +4833,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122721504</v>
+        <v>122719444</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4855,34 +4865,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581165</v>
+        <v>580956</v>
       </c>
       <c r="R39" t="n">
-        <v>7057471</v>
+        <v>7057671</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4912,19 +4922,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4939,22 +4939,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122720478</v>
+        <v>122720911</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4967,21 +4967,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581116</v>
+        <v>581101</v>
       </c>
       <c r="R40" t="n">
-        <v>7057570</v>
+        <v>7057443</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5036,7 +5036,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5051,22 +5056,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122719953</v>
+        <v>122719358</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5079,21 +5084,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5103,10 +5108,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580942</v>
+        <v>580961</v>
       </c>
       <c r="R41" t="n">
-        <v>7057618</v>
+        <v>7057655</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5136,9 +5141,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5153,22 +5168,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122718748</v>
+        <v>122722336</v>
       </c>
       <c r="B42" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5177,31 +5192,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5210,10 +5225,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581004</v>
+        <v>581102</v>
       </c>
       <c r="R42" t="n">
-        <v>7057692</v>
+        <v>7057625</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5245,7 +5260,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5255,7 +5270,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5282,10 +5302,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122719828</v>
+        <v>122722222</v>
       </c>
       <c r="B43" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5294,43 +5314,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580901</v>
+        <v>581129</v>
       </c>
       <c r="R43" t="n">
-        <v>7057649</v>
+        <v>7057634</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5362,7 +5382,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5372,7 +5392,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5387,22 +5412,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122722057</v>
+        <v>122721690</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>91397</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5411,43 +5436,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581149</v>
+        <v>581129</v>
       </c>
       <c r="R44" t="n">
-        <v>7057577</v>
+        <v>7057525</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5479,7 +5499,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5489,12 +5509,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5521,10 +5536,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122720911</v>
+        <v>122721034</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5537,21 +5552,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5561,10 +5576,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581101</v>
+        <v>581112</v>
       </c>
       <c r="R45" t="n">
-        <v>7057443</v>
+        <v>7057450</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5596,7 +5611,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5606,12 +5621,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5626,22 +5636,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122720457</v>
+        <v>122719175</v>
       </c>
       <c r="B46" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5654,42 +5664,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581081</v>
+        <v>580984</v>
       </c>
       <c r="R46" t="n">
-        <v>7057535</v>
+        <v>7057676</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5718,7 +5723,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5728,7 +5733,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5743,22 +5748,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122721690</v>
+        <v>122720257</v>
       </c>
       <c r="B47" t="n">
-        <v>91397</v>
+        <v>78502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5767,38 +5772,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581129</v>
+        <v>580942</v>
       </c>
       <c r="R47" t="n">
-        <v>7057525</v>
+        <v>7057618</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5828,19 +5833,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:37</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5855,22 +5850,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122718678</v>
+        <v>122720546</v>
       </c>
       <c r="B48" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5883,34 +5878,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581005</v>
+        <v>581075</v>
       </c>
       <c r="R48" t="n">
-        <v>7057691</v>
+        <v>7057498</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5952,7 +5952,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5979,10 +5984,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122718574</v>
+        <v>122720366</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5995,21 +6000,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6019,10 +6024,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580996</v>
+        <v>581078</v>
       </c>
       <c r="R49" t="n">
-        <v>7057711</v>
+        <v>7057568</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6054,7 +6059,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6064,7 +6069,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6079,19 +6084,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122720366</v>
+        <v>122720528</v>
       </c>
       <c r="B50" t="n">
         <v>78503</v>
@@ -6131,10 +6136,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581078</v>
+        <v>581073</v>
       </c>
       <c r="R50" t="n">
-        <v>7057568</v>
+        <v>7057503</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6166,7 +6171,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6176,7 +6181,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6191,22 +6196,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122719214</v>
+        <v>122719696</v>
       </c>
       <c r="B51" t="n">
-        <v>56688</v>
+        <v>78411</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6215,46 +6220,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580978</v>
+        <v>580901</v>
       </c>
       <c r="R51" t="n">
-        <v>7057665</v>
+        <v>7057649</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6320,7 +6320,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122720864</v>
+        <v>122721195</v>
       </c>
       <c r="B52" t="n">
         <v>79847</v>
@@ -6360,13 +6360,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581112</v>
+        <v>581116</v>
       </c>
       <c r="R52" t="n">
-        <v>7057450</v>
+        <v>7057434</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6393,19 +6393,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6420,22 +6410,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122721161</v>
+        <v>122721705</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6448,34 +6438,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581208</v>
+        <v>581182</v>
       </c>
       <c r="R53" t="n">
-        <v>7057450</v>
+        <v>7057497</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6507,7 +6497,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6517,7 +6507,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6532,22 +6522,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122719130</v>
+        <v>122720063</v>
       </c>
       <c r="B54" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6560,21 +6550,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6584,10 +6574,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580985</v>
+        <v>580986</v>
       </c>
       <c r="R54" t="n">
-        <v>7057694</v>
+        <v>7057585</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6619,7 +6609,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6629,7 +6619,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6656,7 +6646,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122722473</v>
+        <v>122722537</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6696,10 +6686,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581086</v>
+        <v>581065</v>
       </c>
       <c r="R55" t="n">
-        <v>7057686</v>
+        <v>7057691</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6756,22 +6746,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122720827</v>
+        <v>122720864</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6784,21 +6774,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6808,13 +6798,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581102</v>
+        <v>581112</v>
       </c>
       <c r="R56" t="n">
-        <v>7057553</v>
+        <v>7057450</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6843,7 +6833,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6853,7 +6843,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6880,10 +6870,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122721907</v>
+        <v>122718574</v>
       </c>
       <c r="B57" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6896,39 +6886,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581134</v>
+        <v>580996</v>
       </c>
       <c r="R57" t="n">
-        <v>7057504</v>
+        <v>7057711</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6960,7 +6945,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6970,7 +6955,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6997,10 +6982,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122721757</v>
+        <v>122720096</v>
       </c>
       <c r="B58" t="n">
-        <v>91243</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7013,34 +6998,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581120</v>
+        <v>580942</v>
       </c>
       <c r="R58" t="n">
-        <v>7057493</v>
+        <v>7057618</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7070,21 +7055,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7093,26 +7068,41 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122722222</v>
+        <v>122719411</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7125,42 +7115,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581129</v>
+        <v>580961</v>
       </c>
       <c r="R59" t="n">
-        <v>7057634</v>
+        <v>7057655</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7189,7 +7174,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7199,12 +7184,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7219,19 +7199,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122719358</v>
+        <v>122719963</v>
       </c>
       <c r="B60" t="n">
         <v>78502</v>
@@ -7271,10 +7251,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580961</v>
+        <v>580966</v>
       </c>
       <c r="R60" t="n">
-        <v>7057655</v>
+        <v>7057594</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7306,7 +7286,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7316,7 +7296,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7460,10 +7440,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122721655</v>
+        <v>122719828</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7472,41 +7452,46 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581182</v>
+        <v>580901</v>
       </c>
       <c r="R62" t="n">
-        <v>7057497</v>
+        <v>7057649</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7535,7 +7520,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7545,7 +7530,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7572,10 +7557,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122719400</v>
+        <v>122719214</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7584,41 +7569,46 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580956</v>
+        <v>580978</v>
       </c>
       <c r="R63" t="n">
-        <v>7057671</v>
+        <v>7057665</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7645,9 +7635,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7662,12 +7662,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122719455</v>
+        <v>122720827</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580912</v>
+        <v>581102</v>
       </c>
       <c r="R5" t="n">
-        <v>7057652</v>
+        <v>7057553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122720827</v>
+        <v>122718499</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581102</v>
+        <v>580999</v>
       </c>
       <c r="R6" t="n">
-        <v>7057553</v>
+        <v>7057695</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122718499</v>
+        <v>122719455</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580999</v>
+        <v>580912</v>
       </c>
       <c r="R7" t="n">
-        <v>7057695</v>
+        <v>7057652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,12 +1340,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122720528</v>
+        <v>122721705</v>
       </c>
       <c r="B50" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6112,21 +6112,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581073</v>
+        <v>581182</v>
       </c>
       <c r="R50" t="n">
-        <v>7057503</v>
+        <v>7057497</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6196,12 +6196,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6422,10 +6422,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122721705</v>
+        <v>122720528</v>
       </c>
       <c r="B53" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6438,21 +6438,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581182</v>
+        <v>581073</v>
       </c>
       <c r="R53" t="n">
-        <v>7057497</v>
+        <v>7057503</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6522,12 +6522,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6982,10 +6982,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122720096</v>
+        <v>122719411</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6998,21 +6998,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7022,13 +7022,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580942</v>
+        <v>580961</v>
       </c>
       <c r="R58" t="n">
-        <v>7057618</v>
+        <v>7057655</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7055,11 +7055,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7068,41 +7078,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122719411</v>
+        <v>122722701</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7115,34 +7110,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580961</v>
+        <v>581065</v>
       </c>
       <c r="R59" t="n">
-        <v>7057655</v>
+        <v>7057691</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7211,10 +7211,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122719963</v>
+        <v>122720096</v>
       </c>
       <c r="B60" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7227,21 +7227,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7251,10 +7251,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580966</v>
+        <v>580942</v>
       </c>
       <c r="R60" t="n">
-        <v>7057594</v>
+        <v>7057618</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7284,21 +7284,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7307,26 +7297,41 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122722701</v>
+        <v>122719963</v>
       </c>
       <c r="B61" t="n">
-        <v>57494</v>
+        <v>78502</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7339,42 +7344,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581065</v>
+        <v>580966</v>
       </c>
       <c r="R61" t="n">
-        <v>7057691</v>
+        <v>7057594</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -4513,10 +4513,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122720544</v>
+        <v>122721757</v>
       </c>
       <c r="B36" t="n">
-        <v>78502</v>
+        <v>91243</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4529,21 +4529,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4553,10 +4553,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581116</v>
+        <v>581120</v>
       </c>
       <c r="R36" t="n">
-        <v>7057570</v>
+        <v>7057493</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4613,22 +4613,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122721757</v>
+        <v>122720544</v>
       </c>
       <c r="B37" t="n">
-        <v>91243</v>
+        <v>78502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4641,21 +4641,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581120</v>
+        <v>581116</v>
       </c>
       <c r="R37" t="n">
-        <v>7057493</v>
+        <v>7057570</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4725,12 +4725,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122721705</v>
+        <v>122720528</v>
       </c>
       <c r="B50" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6112,21 +6112,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581182</v>
+        <v>581073</v>
       </c>
       <c r="R50" t="n">
-        <v>7057497</v>
+        <v>7057503</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6196,12 +6196,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6422,10 +6422,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122720528</v>
+        <v>122721705</v>
       </c>
       <c r="B53" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6438,21 +6438,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581073</v>
+        <v>581182</v>
       </c>
       <c r="R53" t="n">
-        <v>7057503</v>
+        <v>7057497</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6522,12 +6522,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122720827</v>
+        <v>122719455</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581102</v>
+        <v>580912</v>
       </c>
       <c r="R5" t="n">
-        <v>7057553</v>
+        <v>7057652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122718499</v>
+        <v>122720827</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580999</v>
+        <v>581102</v>
       </c>
       <c r="R6" t="n">
-        <v>7057695</v>
+        <v>7057553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122719455</v>
+        <v>122718499</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580912</v>
+        <v>580999</v>
       </c>
       <c r="R7" t="n">
-        <v>7057652</v>
+        <v>7057695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,12 +1340,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -5424,10 +5424,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122721690</v>
+        <v>122719175</v>
       </c>
       <c r="B44" t="n">
-        <v>91397</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5436,25 +5436,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5464,13 +5464,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581129</v>
+        <v>580984</v>
       </c>
       <c r="R44" t="n">
-        <v>7057525</v>
+        <v>7057676</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5524,22 +5524,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122721034</v>
+        <v>122720546</v>
       </c>
       <c r="B45" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5552,34 +5552,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581112</v>
+        <v>581075</v>
       </c>
       <c r="R45" t="n">
-        <v>7057450</v>
+        <v>7057498</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5611,7 +5616,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5621,7 +5626,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5636,22 +5646,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122719175</v>
+        <v>122721690</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>91397</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5660,25 +5670,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5688,13 +5698,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580984</v>
+        <v>581129</v>
       </c>
       <c r="R46" t="n">
-        <v>7057676</v>
+        <v>7057525</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5723,7 +5733,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5733,7 +5743,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5748,12 +5758,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5862,10 +5872,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122720546</v>
+        <v>122721034</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5878,39 +5888,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581075</v>
+        <v>581112</v>
       </c>
       <c r="R48" t="n">
-        <v>7057498</v>
+        <v>7057450</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5942,7 +5947,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5952,12 +5957,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5972,12 +5972,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122719455</v>
+        <v>122720827</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580912</v>
+        <v>581102</v>
       </c>
       <c r="R5" t="n">
-        <v>7057652</v>
+        <v>7057553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122720827</v>
+        <v>122718499</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581102</v>
+        <v>580999</v>
       </c>
       <c r="R6" t="n">
-        <v>7057553</v>
+        <v>7057695</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122718499</v>
+        <v>122719455</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580999</v>
+        <v>580912</v>
       </c>
       <c r="R7" t="n">
-        <v>7057695</v>
+        <v>7057652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,12 +1340,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -5424,10 +5424,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122719175</v>
+        <v>122721690</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>91397</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5436,25 +5436,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5464,13 +5464,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580984</v>
+        <v>581129</v>
       </c>
       <c r="R44" t="n">
-        <v>7057676</v>
+        <v>7057525</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5524,22 +5524,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122720546</v>
+        <v>122721034</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5552,39 +5552,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581075</v>
+        <v>581112</v>
       </c>
       <c r="R45" t="n">
-        <v>7057498</v>
+        <v>7057450</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5616,7 +5611,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5626,12 +5621,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5646,22 +5636,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122721690</v>
+        <v>122719175</v>
       </c>
       <c r="B46" t="n">
-        <v>91397</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5670,25 +5660,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5698,13 +5688,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581129</v>
+        <v>580984</v>
       </c>
       <c r="R46" t="n">
-        <v>7057525</v>
+        <v>7057676</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5733,7 +5723,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5743,7 +5733,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5758,12 +5748,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5872,10 +5862,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122721034</v>
+        <v>122720546</v>
       </c>
       <c r="B48" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5888,34 +5878,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581112</v>
+        <v>581075</v>
       </c>
       <c r="R48" t="n">
-        <v>7057450</v>
+        <v>7057498</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5947,7 +5942,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5957,7 +5952,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5972,12 +5972,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122720528</v>
+        <v>122721705</v>
       </c>
       <c r="B50" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6112,21 +6112,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581073</v>
+        <v>581182</v>
       </c>
       <c r="R50" t="n">
-        <v>7057503</v>
+        <v>7057497</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6196,12 +6196,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6422,10 +6422,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122721705</v>
+        <v>122720528</v>
       </c>
       <c r="B53" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6438,21 +6438,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581182</v>
+        <v>581073</v>
       </c>
       <c r="R53" t="n">
-        <v>7057497</v>
+        <v>7057503</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6522,12 +6522,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122721338</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721113</v>
+        <v>122721501</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581208</v>
+        <v>581145</v>
       </c>
       <c r="R3" t="n">
-        <v>7057415</v>
+        <v>7057410</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721501</v>
+        <v>122721113</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,37 +915,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581145</v>
+        <v>581208</v>
       </c>
       <c r="R4" t="n">
-        <v>7057410</v>
+        <v>7057415</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122720827</v>
+        <v>122721757</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>91242</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581102</v>
+        <v>581120</v>
       </c>
       <c r="R5" t="n">
-        <v>7057553</v>
+        <v>7057493</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122718499</v>
+        <v>122719358</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>78505</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580999</v>
+        <v>580961</v>
       </c>
       <c r="R6" t="n">
-        <v>7057695</v>
+        <v>7057655</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122719455</v>
+        <v>122720257</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>78505</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580912</v>
+        <v>580942</v>
       </c>
       <c r="R7" t="n">
-        <v>7057652</v>
+        <v>7057618</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,19 +1313,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,22 +1330,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122721907</v>
+        <v>122718574</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>79850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,39 +1358,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581134</v>
+        <v>580996</v>
       </c>
       <c r="R8" t="n">
-        <v>7057504</v>
+        <v>7057711</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122719600</v>
+        <v>122719444</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>78505</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1555,21 +1540,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1586,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122720361</v>
+        <v>122720457</v>
       </c>
       <c r="B10" t="n">
-        <v>78502</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,37 +1572,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581082</v>
+        <v>581081</v>
       </c>
       <c r="R10" t="n">
-        <v>7057561</v>
+        <v>7057535</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,22 +1661,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122722057</v>
+        <v>122721504</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,39 +1689,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581149</v>
+        <v>581165</v>
       </c>
       <c r="R11" t="n">
-        <v>7057577</v>
+        <v>7057471</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,12 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122722549</v>
+        <v>122720063</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>78505</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581043</v>
+        <v>580986</v>
       </c>
       <c r="R12" t="n">
-        <v>7057689</v>
+        <v>7057585</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122719400</v>
+        <v>122720827</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,14 +1933,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580956</v>
+        <v>581102</v>
       </c>
       <c r="R13" t="n">
-        <v>7057671</v>
+        <v>7057553</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,9 +1970,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,22 +1997,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122719558</v>
+        <v>122722071</v>
       </c>
       <c r="B14" t="n">
-        <v>79848</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,34 +2025,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580907</v>
+        <v>581148</v>
       </c>
       <c r="R14" t="n">
-        <v>7057652</v>
+        <v>7057575</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2099,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,22 +2119,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122720577</v>
+        <v>122719411</v>
       </c>
       <c r="B15" t="n">
-        <v>78411</v>
+        <v>78769</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,37 +2147,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581103</v>
+        <v>580961</v>
       </c>
       <c r="R15" t="n">
-        <v>7057525</v>
+        <v>7057655</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2221,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122718715</v>
+        <v>122719442</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,14 +2279,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581011</v>
+        <v>580912</v>
       </c>
       <c r="R16" t="n">
-        <v>7057695</v>
+        <v>7057652</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,22 +2343,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122719953</v>
+        <v>122721195</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,34 +2371,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580942</v>
+        <v>581116</v>
       </c>
       <c r="R17" t="n">
-        <v>7057618</v>
+        <v>7057434</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,10 +2457,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122721655</v>
+        <v>122720361</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>78505</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,21 +2473,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,13 +2497,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581182</v>
+        <v>581082</v>
       </c>
       <c r="R18" t="n">
-        <v>7057497</v>
+        <v>7057561</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2547,7 +2532,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2542,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122722059</v>
+        <v>122719585</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,34 +2585,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581149</v>
+        <v>580901</v>
       </c>
       <c r="R19" t="n">
-        <v>7057571</v>
+        <v>7057649</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2644,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,12 +2654,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2689,22 +2669,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122722568</v>
+        <v>122720385</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2741,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581036</v>
+        <v>581098</v>
       </c>
       <c r="R20" t="n">
-        <v>7057698</v>
+        <v>7057575</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,22 +2781,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122718678</v>
+        <v>122719953</v>
       </c>
       <c r="B21" t="n">
-        <v>78502</v>
+        <v>78769</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,34 +2809,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581005</v>
+        <v>580942</v>
       </c>
       <c r="R21" t="n">
-        <v>7057691</v>
+        <v>7057618</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2886,19 +2866,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2913,22 +2883,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122718748</v>
+        <v>122720864</v>
       </c>
       <c r="B22" t="n">
-        <v>56688</v>
+        <v>79850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,46 +2907,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581004</v>
+        <v>581112</v>
       </c>
       <c r="R22" t="n">
-        <v>7057692</v>
+        <v>7057450</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3005,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,22 +2995,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122720457</v>
+        <v>122718715</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>79850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3058,39 +3023,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581081</v>
+        <v>581011</v>
       </c>
       <c r="R23" t="n">
-        <v>7057535</v>
+        <v>7057695</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,7 +3082,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3092,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,22 +3107,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122721504</v>
+        <v>122722568</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,21 +3135,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3199,10 +3159,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581165</v>
+        <v>581036</v>
       </c>
       <c r="R24" t="n">
-        <v>7057471</v>
+        <v>7057698</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,7 +3194,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3204,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,22 +3219,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122719585</v>
+        <v>122722059</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3287,34 +3247,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580901</v>
+        <v>581149</v>
       </c>
       <c r="R25" t="n">
-        <v>7057649</v>
+        <v>7057571</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,7 +3306,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3356,7 +3316,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,22 +3336,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122722071</v>
+        <v>122720351</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3399,39 +3364,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581148</v>
+        <v>581082</v>
       </c>
       <c r="R26" t="n">
-        <v>7057575</v>
+        <v>7057561</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,7 +3423,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,12 +3433,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3493,22 +3448,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122719250</v>
+        <v>122722473</v>
       </c>
       <c r="B27" t="n">
-        <v>90952</v>
+        <v>78769</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3521,21 +3476,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3545,10 +3500,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580977</v>
+        <v>581086</v>
       </c>
       <c r="R27" t="n">
-        <v>7057668</v>
+        <v>7057686</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3580,7 +3535,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3590,7 +3545,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,10 +3572,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122720351</v>
+        <v>122719214</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>56691</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3629,41 +3584,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581082</v>
+        <v>580978</v>
       </c>
       <c r="R28" t="n">
-        <v>7057561</v>
+        <v>7057665</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3692,7 +3652,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3662,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,10 +3689,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122719130</v>
+        <v>122719600</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3765,14 +3725,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580985</v>
+        <v>580956</v>
       </c>
       <c r="R29" t="n">
-        <v>7057694</v>
+        <v>7057671</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3802,21 +3762,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3825,26 +3775,41 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122721161</v>
+        <v>122718748</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>56691</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3853,38 +3818,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581208</v>
+        <v>581004</v>
       </c>
       <c r="R30" t="n">
-        <v>7057450</v>
+        <v>7057692</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3916,7 +3886,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3926,7 +3896,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,22 +3911,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122721746</v>
+        <v>122720478</v>
       </c>
       <c r="B31" t="n">
-        <v>91397</v>
+        <v>78769</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3965,25 +3935,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3993,10 +3963,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581131</v>
+        <v>581116</v>
       </c>
       <c r="R31" t="n">
-        <v>7057499</v>
+        <v>7057570</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4028,7 +3998,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4008,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4053,22 +4023,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122720478</v>
+        <v>122719400</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4101,14 +4071,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581116</v>
+        <v>580956</v>
       </c>
       <c r="R32" t="n">
-        <v>7057570</v>
+        <v>7057671</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4138,19 +4108,9 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4165,22 +4125,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122722473</v>
+        <v>122719531</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>79851</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4193,21 +4153,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4217,10 +4177,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581086</v>
+        <v>580913</v>
       </c>
       <c r="R33" t="n">
-        <v>7057686</v>
+        <v>7057655</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4252,7 +4212,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4262,7 +4222,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4289,10 +4249,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122721003</v>
+        <v>122720911</v>
       </c>
       <c r="B34" t="n">
-        <v>78502</v>
+        <v>57481</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4305,21 +4265,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4329,13 +4289,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581112</v>
+        <v>581101</v>
       </c>
       <c r="R34" t="n">
-        <v>7057450</v>
+        <v>7057443</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4364,7 +4324,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4374,7 +4334,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4389,22 +4354,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122719531</v>
+        <v>122721003</v>
       </c>
       <c r="B35" t="n">
-        <v>79848</v>
+        <v>78505</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4417,21 +4382,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4441,13 +4406,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580913</v>
+        <v>581112</v>
       </c>
       <c r="R35" t="n">
-        <v>7057655</v>
+        <v>7057450</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4476,7 +4441,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4486,7 +4451,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4501,22 +4466,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122721757</v>
+        <v>122721907</v>
       </c>
       <c r="B36" t="n">
-        <v>91243</v>
+        <v>57497</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4529,34 +4494,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581120</v>
+        <v>581134</v>
       </c>
       <c r="R36" t="n">
-        <v>7057493</v>
+        <v>7057504</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4588,7 +4558,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4598,7 +4568,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4613,22 +4583,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122720544</v>
+        <v>122718499</v>
       </c>
       <c r="B37" t="n">
-        <v>78502</v>
+        <v>78769</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4641,21 +4611,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4665,10 +4635,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581116</v>
+        <v>580999</v>
       </c>
       <c r="R37" t="n">
-        <v>7057570</v>
+        <v>7057695</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4700,7 +4670,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4710,7 +4680,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4725,22 +4695,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122720458</v>
+        <v>122720546</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4753,34 +4723,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581098</v>
+        <v>581075</v>
       </c>
       <c r="R38" t="n">
-        <v>7057575</v>
+        <v>7057498</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4812,7 +4787,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4822,7 +4797,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4837,22 +4817,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122719444</v>
+        <v>122719963</v>
       </c>
       <c r="B39" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4889,10 +4869,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580956</v>
+        <v>580966</v>
       </c>
       <c r="R39" t="n">
-        <v>7057671</v>
+        <v>7057594</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4922,9 +4902,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4939,22 +4929,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122720911</v>
+        <v>122721161</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4967,34 +4957,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581101</v>
+        <v>581208</v>
       </c>
       <c r="R40" t="n">
-        <v>7057443</v>
+        <v>7057450</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5026,7 +5016,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5036,12 +5026,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5068,10 +5053,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122719358</v>
+        <v>122718678</v>
       </c>
       <c r="B41" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5104,14 +5089,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580961</v>
+        <v>581005</v>
       </c>
       <c r="R41" t="n">
-        <v>7057655</v>
+        <v>7057691</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5143,7 +5128,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5138,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5168,22 +5153,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122722336</v>
+        <v>122719250</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5196,39 +5181,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581102</v>
+        <v>580977</v>
       </c>
       <c r="R42" t="n">
-        <v>7057625</v>
+        <v>7057668</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5260,7 +5240,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5270,12 +5250,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5302,10 +5277,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122722222</v>
+        <v>122719828</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>56691</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5314,43 +5289,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581129</v>
+        <v>580901</v>
       </c>
       <c r="R43" t="n">
-        <v>7057634</v>
+        <v>7057649</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5382,7 +5357,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5392,12 +5367,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5412,22 +5382,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122721690</v>
+        <v>122722336</v>
       </c>
       <c r="B44" t="n">
-        <v>91397</v>
+        <v>57481</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5436,38 +5406,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581129</v>
+        <v>581102</v>
       </c>
       <c r="R44" t="n">
-        <v>7057525</v>
+        <v>7057625</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5499,7 +5474,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5509,7 +5484,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5536,10 +5516,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122721034</v>
+        <v>122722222</v>
       </c>
       <c r="B45" t="n">
-        <v>78503</v>
+        <v>57481</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5552,34 +5532,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581112</v>
+        <v>581129</v>
       </c>
       <c r="R45" t="n">
-        <v>7057450</v>
+        <v>7057634</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5611,7 +5596,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5621,7 +5606,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5636,22 +5626,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122719175</v>
+        <v>122721655</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5688,13 +5678,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580984</v>
+        <v>581182</v>
       </c>
       <c r="R46" t="n">
-        <v>7057676</v>
+        <v>7057497</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5723,7 +5713,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5733,7 +5723,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5760,10 +5750,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122720257</v>
+        <v>122722057</v>
       </c>
       <c r="B47" t="n">
-        <v>78502</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5776,34 +5766,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580942</v>
+        <v>581149</v>
       </c>
       <c r="R47" t="n">
-        <v>7057618</v>
+        <v>7057577</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5833,9 +5828,24 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5850,22 +5860,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122720546</v>
+        <v>122721034</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>78506</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5878,39 +5888,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581075</v>
+        <v>581112</v>
       </c>
       <c r="R48" t="n">
-        <v>7057498</v>
+        <v>7057450</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5942,7 +5947,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5952,12 +5957,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5972,22 +5972,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122720366</v>
+        <v>122721705</v>
       </c>
       <c r="B49" t="n">
-        <v>78503</v>
+        <v>78505</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6000,21 +6000,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581078</v>
+        <v>581182</v>
       </c>
       <c r="R49" t="n">
-        <v>7057568</v>
+        <v>7057497</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,10 +6096,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122721705</v>
+        <v>122720096</v>
       </c>
       <c r="B50" t="n">
-        <v>78502</v>
+        <v>79850</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6112,34 +6112,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581182</v>
+        <v>580942</v>
       </c>
       <c r="R50" t="n">
-        <v>7057497</v>
+        <v>7057618</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6169,21 +6169,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6192,26 +6182,41 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122719696</v>
+        <v>122722537</v>
       </c>
       <c r="B51" t="n">
-        <v>78411</v>
+        <v>78769</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6224,34 +6229,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580901</v>
+        <v>581065</v>
       </c>
       <c r="R51" t="n">
-        <v>7057649</v>
+        <v>7057691</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6283,7 +6288,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6293,7 +6298,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6320,10 +6325,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122721195</v>
+        <v>122720577</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>78414</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6336,21 +6341,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6360,10 +6365,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581116</v>
+        <v>581103</v>
       </c>
       <c r="R52" t="n">
-        <v>7057434</v>
+        <v>7057525</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6393,9 +6398,19 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6410,22 +6425,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122720528</v>
+        <v>122719696</v>
       </c>
       <c r="B53" t="n">
-        <v>78503</v>
+        <v>78414</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6438,34 +6453,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Taråbergen, Taråbergen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581073</v>
+        <v>580901</v>
       </c>
       <c r="R53" t="n">
-        <v>7057503</v>
+        <v>7057649</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6497,7 +6512,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6507,7 +6522,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6522,22 +6537,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122720063</v>
+        <v>122720544</v>
       </c>
       <c r="B54" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6574,10 +6589,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580986</v>
+        <v>581116</v>
       </c>
       <c r="R54" t="n">
-        <v>7057585</v>
+        <v>7057570</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6609,7 +6624,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6619,7 +6634,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6634,22 +6649,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122722537</v>
+        <v>122719130</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6662,21 +6677,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6686,10 +6701,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581065</v>
+        <v>580985</v>
       </c>
       <c r="R55" t="n">
-        <v>7057691</v>
+        <v>7057694</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6721,7 +6736,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6731,7 +6746,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6746,22 +6761,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122720864</v>
+        <v>122721746</v>
       </c>
       <c r="B56" t="n">
-        <v>79847</v>
+        <v>91400</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6770,25 +6785,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6798,13 +6813,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581112</v>
+        <v>581131</v>
       </c>
       <c r="R56" t="n">
-        <v>7057450</v>
+        <v>7057499</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6833,7 +6848,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6843,7 +6858,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6858,22 +6873,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122718574</v>
+        <v>122721690</v>
       </c>
       <c r="B57" t="n">
-        <v>79847</v>
+        <v>91400</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6882,25 +6897,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6910,10 +6925,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>580996</v>
+        <v>581129</v>
       </c>
       <c r="R57" t="n">
-        <v>7057711</v>
+        <v>7057525</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6945,7 +6960,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6955,7 +6970,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6982,10 +6997,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122719411</v>
+        <v>122719175</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7018,14 +7033,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580961</v>
+        <v>580984</v>
       </c>
       <c r="R58" t="n">
-        <v>7057655</v>
+        <v>7057676</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7057,7 +7072,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7067,7 +7082,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7097,7 +7112,7 @@
         <v>122722701</v>
       </c>
       <c r="B59" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7211,10 +7226,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122720096</v>
+        <v>122719558</v>
       </c>
       <c r="B60" t="n">
-        <v>79847</v>
+        <v>79851</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7227,21 +7242,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7251,10 +7266,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580942</v>
+        <v>580907</v>
       </c>
       <c r="R60" t="n">
-        <v>7057618</v>
+        <v>7057652</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7284,11 +7299,21 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7297,41 +7322,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122719963</v>
+        <v>122720528</v>
       </c>
       <c r="B61" t="n">
-        <v>78502</v>
+        <v>78506</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7344,34 +7354,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580966</v>
+        <v>581073</v>
       </c>
       <c r="R61" t="n">
-        <v>7057594</v>
+        <v>7057503</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7403,7 +7413,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7413,7 +7423,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7428,22 +7438,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122719828</v>
+        <v>122720366</v>
       </c>
       <c r="B62" t="n">
-        <v>56688</v>
+        <v>78506</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7452,43 +7462,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Taråbergen, Taråbergen, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580901</v>
+        <v>581078</v>
       </c>
       <c r="R62" t="n">
-        <v>7057649</v>
+        <v>7057568</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7520,7 +7525,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7530,7 +7535,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7557,10 +7562,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122719214</v>
+        <v>122722549</v>
       </c>
       <c r="B63" t="n">
-        <v>56688</v>
+        <v>78769</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7569,46 +7574,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580978</v>
+        <v>581043</v>
       </c>
       <c r="R63" t="n">
-        <v>7057665</v>
+        <v>7057689</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7662,12 +7662,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7672,6 +7672,127 @@
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129309000</v>
+      </c>
+      <c r="B64" t="n">
+        <v>56920</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Tarå, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>581087</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7057644</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -7677,7 +7677,7 @@
         <v>129309000</v>
       </c>
       <c r="B64" t="n">
-        <v>56920</v>
+        <v>56923</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -7677,7 +7677,7 @@
         <v>129309000</v>
       </c>
       <c r="B64" t="n">
-        <v>56923</v>
+        <v>56928</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -7677,7 +7677,7 @@
         <v>129309000</v>
       </c>
       <c r="B64" t="n">
-        <v>56928</v>
+        <v>56929</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -7677,7 +7677,7 @@
         <v>129309000</v>
       </c>
       <c r="B64" t="n">
-        <v>56929</v>
+        <v>56930</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 3639-2025 artfynd.xlsx
+++ b/artfynd/A 3639-2025 artfynd.xlsx
@@ -7677,7 +7677,7 @@
         <v>129309000</v>
       </c>
       <c r="B64" t="n">
-        <v>56930</v>
+        <v>56933</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
